--- a/docs/Gestão do Projeto.xlsx
+++ b/docs/Gestão do Projeto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexandre.aneves\Documents\Alexandre Neves\2026\2026_2\Design de Software\Robô Desvia Obstáculo\Documentos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="293" documentId="13_ncr:1_{0D96AE51-37FE-48D1-8181-D46899D8BCB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD10ACBE-747C-47F6-80C9-D2C1F9FC8806}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E07579F-AE2F-405A-84F9-41C015151A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="816" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="816" firstSheet="5" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Visão Geral" sheetId="1" r:id="rId1"/>
@@ -2232,23 +2232,26 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2265,38 +2268,35 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3315,12 +3315,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
     </row>
     <row r="2" spans="1:4" ht="6" customHeight="1">
       <c r="A2" s="76"/>
@@ -3385,28 +3385,28 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
     </row>
     <row r="9" spans="1:4" ht="39.75" customHeight="1">
-      <c r="A9" s="56" t="s">
+      <c r="A9" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="56"/>
-      <c r="C9" s="56"/>
-      <c r="D9" s="56"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1">
-      <c r="A11" s="64" t="s">
+      <c r="A11" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
     </row>
     <row r="12" spans="1:4" ht="21.75" customHeight="1">
       <c r="A12" s="5" t="s">
@@ -3620,17 +3620,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="53" t="s">
         <v>432</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
     </row>
     <row r="2" spans="1:9" ht="6" customHeight="1">
       <c r="A2" s="76"/>
@@ -4055,15 +4055,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="53" t="s">
         <v>480</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
     </row>
     <row r="2" spans="1:7" ht="6" customHeight="1">
       <c r="A2" s="76"/>
@@ -4351,15 +4351,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="53" t="s">
         <v>500</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
     </row>
     <row r="2" spans="1:7" ht="6" customHeight="1">
       <c r="A2" s="76"/>
@@ -4589,290 +4589,290 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:138" ht="27.75" customHeight="1">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="52"/>
-      <c r="V1" s="52"/>
-      <c r="W1" s="52"/>
-      <c r="X1" s="52"/>
-      <c r="Y1" s="52"/>
-      <c r="Z1" s="52"/>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="52"/>
-      <c r="AC1" s="52"/>
-      <c r="AD1" s="52"/>
-      <c r="AE1" s="52"/>
-      <c r="AF1" s="52"/>
-      <c r="AG1" s="52"/>
-      <c r="AH1" s="52"/>
-      <c r="AI1" s="52"/>
-      <c r="AJ1" s="52"/>
-      <c r="AK1" s="52"/>
-      <c r="AL1" s="52"/>
-      <c r="AM1" s="52"/>
-      <c r="AN1" s="52"/>
-      <c r="AO1" s="52"/>
-      <c r="AP1" s="52"/>
-      <c r="AQ1" s="52"/>
-      <c r="AR1" s="52"/>
-      <c r="AS1" s="52"/>
-      <c r="AT1" s="52"/>
-      <c r="AU1" s="52"/>
-      <c r="AV1" s="52"/>
-      <c r="AW1" s="52"/>
-      <c r="AX1" s="52"/>
-      <c r="AY1" s="52"/>
-      <c r="AZ1" s="52"/>
-      <c r="BA1" s="52"/>
-      <c r="BB1" s="52"/>
-      <c r="BC1" s="52"/>
-      <c r="BD1" s="52"/>
-      <c r="BE1" s="52"/>
-      <c r="BF1" s="52"/>
-      <c r="BG1" s="52"/>
-      <c r="BH1" s="52"/>
-      <c r="BI1" s="52"/>
-      <c r="BJ1" s="52"/>
-      <c r="BK1" s="52"/>
-      <c r="BL1" s="52"/>
-      <c r="BM1" s="52"/>
-      <c r="BN1" s="52"/>
-      <c r="BO1" s="52"/>
-      <c r="BP1" s="52"/>
-      <c r="BQ1" s="52"/>
-      <c r="BR1" s="52"/>
-      <c r="BS1" s="52"/>
-      <c r="BT1" s="52"/>
-      <c r="BU1" s="52"/>
-      <c r="BV1" s="52"/>
-      <c r="BW1" s="52"/>
-      <c r="BX1" s="52"/>
-      <c r="BY1" s="52"/>
-      <c r="BZ1" s="52"/>
-      <c r="CA1" s="52"/>
-      <c r="CB1" s="52"/>
-      <c r="CC1" s="52"/>
-      <c r="CD1" s="52"/>
-      <c r="CE1" s="52"/>
-      <c r="CF1" s="52"/>
-      <c r="CG1" s="52"/>
-      <c r="CH1" s="52"/>
-      <c r="CI1" s="52"/>
-      <c r="CJ1" s="52"/>
-      <c r="CK1" s="52"/>
-      <c r="CL1" s="52"/>
-      <c r="CM1" s="52"/>
-      <c r="CN1" s="52"/>
-      <c r="CO1" s="52"/>
-      <c r="CP1" s="52"/>
-      <c r="CQ1" s="52"/>
-      <c r="CR1" s="52"/>
-      <c r="CS1" s="52"/>
-      <c r="CT1" s="52"/>
-      <c r="CU1" s="52"/>
-      <c r="CV1" s="52"/>
-      <c r="CW1" s="52"/>
-      <c r="CX1" s="52"/>
-      <c r="CY1" s="52"/>
-      <c r="CZ1" s="52"/>
-      <c r="DA1" s="52"/>
-      <c r="DB1" s="52"/>
-      <c r="DC1" s="52"/>
-      <c r="DD1" s="52"/>
-      <c r="DE1" s="52"/>
-      <c r="DF1" s="52"/>
-      <c r="DG1" s="52"/>
-      <c r="DH1" s="52"/>
-      <c r="DI1" s="52"/>
-      <c r="DJ1" s="52"/>
-      <c r="DK1" s="52"/>
-      <c r="DL1" s="52"/>
-      <c r="DM1" s="52"/>
-      <c r="DN1" s="52"/>
-      <c r="DO1" s="52"/>
-      <c r="DP1" s="52"/>
-      <c r="DQ1" s="52"/>
-      <c r="DR1" s="52"/>
-      <c r="DS1" s="52"/>
-      <c r="DT1" s="52"/>
-      <c r="DU1" s="52"/>
-      <c r="DV1" s="52"/>
-      <c r="DW1" s="52"/>
-      <c r="DX1" s="52"/>
-      <c r="DY1" s="52"/>
-      <c r="DZ1" s="52"/>
-      <c r="EA1" s="52"/>
-      <c r="EB1" s="52"/>
-      <c r="EC1" s="52"/>
-      <c r="ED1" s="52"/>
-      <c r="EE1" s="52"/>
-      <c r="EF1" s="52"/>
-      <c r="EG1" s="52"/>
-      <c r="EH1" s="52"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
+      <c r="U1" s="67"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="67"/>
+      <c r="X1" s="67"/>
+      <c r="Y1" s="67"/>
+      <c r="Z1" s="67"/>
+      <c r="AA1" s="67"/>
+      <c r="AB1" s="67"/>
+      <c r="AC1" s="67"/>
+      <c r="AD1" s="67"/>
+      <c r="AE1" s="67"/>
+      <c r="AF1" s="67"/>
+      <c r="AG1" s="67"/>
+      <c r="AH1" s="67"/>
+      <c r="AI1" s="67"/>
+      <c r="AJ1" s="67"/>
+      <c r="AK1" s="67"/>
+      <c r="AL1" s="67"/>
+      <c r="AM1" s="67"/>
+      <c r="AN1" s="67"/>
+      <c r="AO1" s="67"/>
+      <c r="AP1" s="67"/>
+      <c r="AQ1" s="67"/>
+      <c r="AR1" s="67"/>
+      <c r="AS1" s="67"/>
+      <c r="AT1" s="67"/>
+      <c r="AU1" s="67"/>
+      <c r="AV1" s="67"/>
+      <c r="AW1" s="67"/>
+      <c r="AX1" s="67"/>
+      <c r="AY1" s="67"/>
+      <c r="AZ1" s="67"/>
+      <c r="BA1" s="67"/>
+      <c r="BB1" s="67"/>
+      <c r="BC1" s="67"/>
+      <c r="BD1" s="67"/>
+      <c r="BE1" s="67"/>
+      <c r="BF1" s="67"/>
+      <c r="BG1" s="67"/>
+      <c r="BH1" s="67"/>
+      <c r="BI1" s="67"/>
+      <c r="BJ1" s="67"/>
+      <c r="BK1" s="67"/>
+      <c r="BL1" s="67"/>
+      <c r="BM1" s="67"/>
+      <c r="BN1" s="67"/>
+      <c r="BO1" s="67"/>
+      <c r="BP1" s="67"/>
+      <c r="BQ1" s="67"/>
+      <c r="BR1" s="67"/>
+      <c r="BS1" s="67"/>
+      <c r="BT1" s="67"/>
+      <c r="BU1" s="67"/>
+      <c r="BV1" s="67"/>
+      <c r="BW1" s="67"/>
+      <c r="BX1" s="67"/>
+      <c r="BY1" s="67"/>
+      <c r="BZ1" s="67"/>
+      <c r="CA1" s="67"/>
+      <c r="CB1" s="67"/>
+      <c r="CC1" s="67"/>
+      <c r="CD1" s="67"/>
+      <c r="CE1" s="67"/>
+      <c r="CF1" s="67"/>
+      <c r="CG1" s="67"/>
+      <c r="CH1" s="67"/>
+      <c r="CI1" s="67"/>
+      <c r="CJ1" s="67"/>
+      <c r="CK1" s="67"/>
+      <c r="CL1" s="67"/>
+      <c r="CM1" s="67"/>
+      <c r="CN1" s="67"/>
+      <c r="CO1" s="67"/>
+      <c r="CP1" s="67"/>
+      <c r="CQ1" s="67"/>
+      <c r="CR1" s="67"/>
+      <c r="CS1" s="67"/>
+      <c r="CT1" s="67"/>
+      <c r="CU1" s="67"/>
+      <c r="CV1" s="67"/>
+      <c r="CW1" s="67"/>
+      <c r="CX1" s="67"/>
+      <c r="CY1" s="67"/>
+      <c r="CZ1" s="67"/>
+      <c r="DA1" s="67"/>
+      <c r="DB1" s="67"/>
+      <c r="DC1" s="67"/>
+      <c r="DD1" s="67"/>
+      <c r="DE1" s="67"/>
+      <c r="DF1" s="67"/>
+      <c r="DG1" s="67"/>
+      <c r="DH1" s="67"/>
+      <c r="DI1" s="67"/>
+      <c r="DJ1" s="67"/>
+      <c r="DK1" s="67"/>
+      <c r="DL1" s="67"/>
+      <c r="DM1" s="67"/>
+      <c r="DN1" s="67"/>
+      <c r="DO1" s="67"/>
+      <c r="DP1" s="67"/>
+      <c r="DQ1" s="67"/>
+      <c r="DR1" s="67"/>
+      <c r="DS1" s="67"/>
+      <c r="DT1" s="67"/>
+      <c r="DU1" s="67"/>
+      <c r="DV1" s="67"/>
+      <c r="DW1" s="67"/>
+      <c r="DX1" s="67"/>
+      <c r="DY1" s="67"/>
+      <c r="DZ1" s="67"/>
+      <c r="EA1" s="67"/>
+      <c r="EB1" s="67"/>
+      <c r="EC1" s="67"/>
+      <c r="ED1" s="67"/>
+      <c r="EE1" s="67"/>
+      <c r="EF1" s="67"/>
+      <c r="EG1" s="67"/>
+      <c r="EH1" s="67"/>
     </row>
     <row r="2" spans="1:138" ht="18" customHeight="1">
-      <c r="G2" s="53" t="s">
+      <c r="G2" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="53"/>
-      <c r="R2" s="53"/>
-      <c r="S2" s="53"/>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
-      <c r="V2" s="53"/>
-      <c r="W2" s="53"/>
-      <c r="X2" s="53"/>
-      <c r="Y2" s="53"/>
-      <c r="Z2" s="53"/>
-      <c r="AA2" s="53"/>
-      <c r="AB2" s="53"/>
-      <c r="AC2" s="53"/>
-      <c r="AD2" s="53"/>
-      <c r="AE2" s="53"/>
-      <c r="AF2" s="53"/>
-      <c r="AG2" s="53"/>
-      <c r="AH2" s="53"/>
-      <c r="AI2" s="53"/>
-      <c r="AJ2" s="53"/>
-      <c r="AK2" s="53"/>
-      <c r="AL2" s="53" t="s">
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="68"/>
+      <c r="P2" s="68"/>
+      <c r="Q2" s="68"/>
+      <c r="R2" s="68"/>
+      <c r="S2" s="68"/>
+      <c r="T2" s="68"/>
+      <c r="U2" s="68"/>
+      <c r="V2" s="68"/>
+      <c r="W2" s="68"/>
+      <c r="X2" s="68"/>
+      <c r="Y2" s="68"/>
+      <c r="Z2" s="68"/>
+      <c r="AA2" s="68"/>
+      <c r="AB2" s="68"/>
+      <c r="AC2" s="68"/>
+      <c r="AD2" s="68"/>
+      <c r="AE2" s="68"/>
+      <c r="AF2" s="68"/>
+      <c r="AG2" s="68"/>
+      <c r="AH2" s="68"/>
+      <c r="AI2" s="68"/>
+      <c r="AJ2" s="68"/>
+      <c r="AK2" s="68"/>
+      <c r="AL2" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="AM2" s="53"/>
-      <c r="AN2" s="53"/>
-      <c r="AO2" s="53"/>
-      <c r="AP2" s="53"/>
-      <c r="AQ2" s="53"/>
-      <c r="AR2" s="53"/>
-      <c r="AS2" s="53"/>
-      <c r="AT2" s="53"/>
-      <c r="AU2" s="53"/>
-      <c r="AV2" s="53"/>
-      <c r="AW2" s="53"/>
-      <c r="AX2" s="53"/>
-      <c r="AY2" s="53"/>
-      <c r="AZ2" s="53"/>
-      <c r="BA2" s="53"/>
-      <c r="BB2" s="53"/>
-      <c r="BC2" s="53"/>
-      <c r="BD2" s="53"/>
-      <c r="BE2" s="53"/>
-      <c r="BF2" s="53"/>
-      <c r="BG2" s="53"/>
-      <c r="BH2" s="53"/>
-      <c r="BI2" s="53"/>
-      <c r="BJ2" s="53"/>
-      <c r="BK2" s="53"/>
-      <c r="BL2" s="53"/>
-      <c r="BM2" s="53"/>
-      <c r="BN2" s="53"/>
-      <c r="BO2" s="53"/>
-      <c r="BP2" s="53" t="s">
+      <c r="AM2" s="68"/>
+      <c r="AN2" s="68"/>
+      <c r="AO2" s="68"/>
+      <c r="AP2" s="68"/>
+      <c r="AQ2" s="68"/>
+      <c r="AR2" s="68"/>
+      <c r="AS2" s="68"/>
+      <c r="AT2" s="68"/>
+      <c r="AU2" s="68"/>
+      <c r="AV2" s="68"/>
+      <c r="AW2" s="68"/>
+      <c r="AX2" s="68"/>
+      <c r="AY2" s="68"/>
+      <c r="AZ2" s="68"/>
+      <c r="BA2" s="68"/>
+      <c r="BB2" s="68"/>
+      <c r="BC2" s="68"/>
+      <c r="BD2" s="68"/>
+      <c r="BE2" s="68"/>
+      <c r="BF2" s="68"/>
+      <c r="BG2" s="68"/>
+      <c r="BH2" s="68"/>
+      <c r="BI2" s="68"/>
+      <c r="BJ2" s="68"/>
+      <c r="BK2" s="68"/>
+      <c r="BL2" s="68"/>
+      <c r="BM2" s="68"/>
+      <c r="BN2" s="68"/>
+      <c r="BO2" s="68"/>
+      <c r="BP2" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="BQ2" s="53"/>
-      <c r="BR2" s="53"/>
-      <c r="BS2" s="53"/>
-      <c r="BT2" s="53"/>
-      <c r="BU2" s="53"/>
-      <c r="BV2" s="53"/>
-      <c r="BW2" s="53"/>
-      <c r="BX2" s="53"/>
-      <c r="BY2" s="53"/>
-      <c r="BZ2" s="53"/>
-      <c r="CA2" s="53"/>
-      <c r="CB2" s="53"/>
-      <c r="CC2" s="53"/>
-      <c r="CD2" s="53"/>
-      <c r="CE2" s="53"/>
-      <c r="CF2" s="53"/>
-      <c r="CG2" s="53"/>
-      <c r="CH2" s="53"/>
-      <c r="CI2" s="53"/>
-      <c r="CJ2" s="53"/>
-      <c r="CK2" s="53"/>
-      <c r="CL2" s="53"/>
-      <c r="CM2" s="53"/>
-      <c r="CN2" s="53"/>
-      <c r="CO2" s="53"/>
-      <c r="CP2" s="53"/>
-      <c r="CQ2" s="53"/>
-      <c r="CR2" s="53"/>
-      <c r="CS2" s="53"/>
-      <c r="CT2" s="53"/>
-      <c r="CU2" s="53" t="s">
+      <c r="BQ2" s="68"/>
+      <c r="BR2" s="68"/>
+      <c r="BS2" s="68"/>
+      <c r="BT2" s="68"/>
+      <c r="BU2" s="68"/>
+      <c r="BV2" s="68"/>
+      <c r="BW2" s="68"/>
+      <c r="BX2" s="68"/>
+      <c r="BY2" s="68"/>
+      <c r="BZ2" s="68"/>
+      <c r="CA2" s="68"/>
+      <c r="CB2" s="68"/>
+      <c r="CC2" s="68"/>
+      <c r="CD2" s="68"/>
+      <c r="CE2" s="68"/>
+      <c r="CF2" s="68"/>
+      <c r="CG2" s="68"/>
+      <c r="CH2" s="68"/>
+      <c r="CI2" s="68"/>
+      <c r="CJ2" s="68"/>
+      <c r="CK2" s="68"/>
+      <c r="CL2" s="68"/>
+      <c r="CM2" s="68"/>
+      <c r="CN2" s="68"/>
+      <c r="CO2" s="68"/>
+      <c r="CP2" s="68"/>
+      <c r="CQ2" s="68"/>
+      <c r="CR2" s="68"/>
+      <c r="CS2" s="68"/>
+      <c r="CT2" s="68"/>
+      <c r="CU2" s="68" t="s">
         <v>67</v>
       </c>
-      <c r="CV2" s="53"/>
-      <c r="CW2" s="53"/>
-      <c r="CX2" s="53"/>
-      <c r="CY2" s="53"/>
-      <c r="CZ2" s="53"/>
-      <c r="DA2" s="53"/>
-      <c r="DB2" s="53"/>
-      <c r="DC2" s="53"/>
-      <c r="DD2" s="53"/>
-      <c r="DE2" s="53"/>
-      <c r="DF2" s="53"/>
-      <c r="DG2" s="53"/>
-      <c r="DH2" s="53"/>
-      <c r="DI2" s="53"/>
-      <c r="DJ2" s="53"/>
-      <c r="DK2" s="53"/>
-      <c r="DL2" s="53"/>
-      <c r="DM2" s="53"/>
-      <c r="DN2" s="53"/>
-      <c r="DO2" s="53"/>
-      <c r="DP2" s="53"/>
-      <c r="DQ2" s="53"/>
-      <c r="DR2" s="53"/>
-      <c r="DS2" s="53"/>
-      <c r="DT2" s="53"/>
-      <c r="DU2" s="53"/>
-      <c r="DV2" s="53"/>
-      <c r="DW2" s="53"/>
-      <c r="DX2" s="53"/>
-      <c r="DY2" s="53" t="s">
+      <c r="CV2" s="68"/>
+      <c r="CW2" s="68"/>
+      <c r="CX2" s="68"/>
+      <c r="CY2" s="68"/>
+      <c r="CZ2" s="68"/>
+      <c r="DA2" s="68"/>
+      <c r="DB2" s="68"/>
+      <c r="DC2" s="68"/>
+      <c r="DD2" s="68"/>
+      <c r="DE2" s="68"/>
+      <c r="DF2" s="68"/>
+      <c r="DG2" s="68"/>
+      <c r="DH2" s="68"/>
+      <c r="DI2" s="68"/>
+      <c r="DJ2" s="68"/>
+      <c r="DK2" s="68"/>
+      <c r="DL2" s="68"/>
+      <c r="DM2" s="68"/>
+      <c r="DN2" s="68"/>
+      <c r="DO2" s="68"/>
+      <c r="DP2" s="68"/>
+      <c r="DQ2" s="68"/>
+      <c r="DR2" s="68"/>
+      <c r="DS2" s="68"/>
+      <c r="DT2" s="68"/>
+      <c r="DU2" s="68"/>
+      <c r="DV2" s="68"/>
+      <c r="DW2" s="68"/>
+      <c r="DX2" s="68"/>
+      <c r="DY2" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="DZ2" s="53"/>
-      <c r="EA2" s="53"/>
-      <c r="EB2" s="53"/>
-      <c r="EC2" s="53"/>
-      <c r="ED2" s="53"/>
-      <c r="EE2" s="53"/>
-      <c r="EF2" s="53"/>
-      <c r="EG2" s="53"/>
-      <c r="EH2" s="53"/>
+      <c r="DZ2" s="68"/>
+      <c r="EA2" s="68"/>
+      <c r="EB2" s="68"/>
+      <c r="EC2" s="68"/>
+      <c r="ED2" s="68"/>
+      <c r="EE2" s="68"/>
+      <c r="EF2" s="68"/>
+      <c r="EG2" s="68"/>
+      <c r="EH2" s="68"/>
     </row>
     <row r="3" spans="1:138" ht="30" customHeight="1">
       <c r="A3" s="5" t="s">
@@ -5291,155 +5291,155 @@
       </c>
     </row>
     <row r="4" spans="1:138" ht="15.75" customHeight="1">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="54"/>
-      <c r="T4" s="54"/>
-      <c r="U4" s="54"/>
-      <c r="V4" s="54"/>
-      <c r="W4" s="54"/>
-      <c r="X4" s="54"/>
-      <c r="Y4" s="54"/>
-      <c r="Z4" s="54"/>
-      <c r="AA4" s="54"/>
-      <c r="AB4" s="54"/>
-      <c r="AC4" s="54"/>
-      <c r="AD4" s="54"/>
-      <c r="AE4" s="54"/>
-      <c r="AF4" s="54"/>
-      <c r="AG4" s="54"/>
-      <c r="AH4" s="54"/>
-      <c r="AI4" s="54"/>
-      <c r="AJ4" s="54"/>
-      <c r="AK4" s="54"/>
-      <c r="AL4" s="54"/>
-      <c r="AM4" s="54"/>
-      <c r="AN4" s="54"/>
-      <c r="AO4" s="54"/>
-      <c r="AP4" s="54"/>
-      <c r="AQ4" s="54"/>
-      <c r="AR4" s="54"/>
-      <c r="AS4" s="54"/>
-      <c r="AT4" s="54"/>
-      <c r="AU4" s="54"/>
-      <c r="AV4" s="54"/>
-      <c r="AW4" s="54"/>
-      <c r="AX4" s="54"/>
-      <c r="AY4" s="54"/>
-      <c r="AZ4" s="54"/>
-      <c r="BA4" s="54"/>
-      <c r="BB4" s="54"/>
-      <c r="BC4" s="54"/>
-      <c r="BD4" s="54"/>
-      <c r="BE4" s="54"/>
-      <c r="BF4" s="54"/>
-      <c r="BG4" s="54"/>
-      <c r="BH4" s="54"/>
-      <c r="BI4" s="54"/>
-      <c r="BJ4" s="54"/>
-      <c r="BK4" s="54"/>
-      <c r="BL4" s="54"/>
-      <c r="BM4" s="54"/>
-      <c r="BN4" s="54"/>
-      <c r="BO4" s="54"/>
-      <c r="BP4" s="54"/>
-      <c r="BQ4" s="54"/>
-      <c r="BR4" s="54"/>
-      <c r="BS4" s="54"/>
-      <c r="BT4" s="54"/>
-      <c r="BU4" s="54"/>
-      <c r="BV4" s="54"/>
-      <c r="BW4" s="54"/>
-      <c r="BX4" s="54"/>
-      <c r="BY4" s="54"/>
-      <c r="BZ4" s="54"/>
-      <c r="CA4" s="54"/>
-      <c r="CB4" s="54"/>
-      <c r="CC4" s="54"/>
-      <c r="CD4" s="54"/>
-      <c r="CE4" s="54"/>
-      <c r="CF4" s="54"/>
-      <c r="CG4" s="54"/>
-      <c r="CH4" s="54"/>
-      <c r="CI4" s="54"/>
-      <c r="CJ4" s="54"/>
-      <c r="CK4" s="54"/>
-      <c r="CL4" s="54"/>
-      <c r="CM4" s="54"/>
-      <c r="CN4" s="54"/>
-      <c r="CO4" s="54"/>
-      <c r="CP4" s="54"/>
-      <c r="CQ4" s="54"/>
-      <c r="CR4" s="54"/>
-      <c r="CS4" s="54"/>
-      <c r="CT4" s="54"/>
-      <c r="CU4" s="54"/>
-      <c r="CV4" s="54"/>
-      <c r="CW4" s="54"/>
-      <c r="CX4" s="54"/>
-      <c r="CY4" s="54"/>
-      <c r="CZ4" s="54"/>
-      <c r="DA4" s="54"/>
-      <c r="DB4" s="54"/>
-      <c r="DC4" s="54"/>
-      <c r="DD4" s="54"/>
-      <c r="DE4" s="54"/>
-      <c r="DF4" s="54"/>
-      <c r="DG4" s="54"/>
-      <c r="DH4" s="54"/>
-      <c r="DI4" s="54"/>
-      <c r="DJ4" s="54"/>
-      <c r="DK4" s="54"/>
-      <c r="DL4" s="54"/>
-      <c r="DM4" s="54"/>
-      <c r="DN4" s="54"/>
-      <c r="DO4" s="54"/>
-      <c r="DP4" s="54"/>
-      <c r="DQ4" s="54"/>
-      <c r="DR4" s="54"/>
-      <c r="DS4" s="54"/>
-      <c r="DT4" s="54"/>
-      <c r="DU4" s="54"/>
-      <c r="DV4" s="54"/>
-      <c r="DW4" s="54"/>
-      <c r="DX4" s="54"/>
-      <c r="DY4" s="54"/>
-      <c r="DZ4" s="54"/>
-      <c r="EA4" s="54"/>
-      <c r="EB4" s="54"/>
-      <c r="EC4" s="54"/>
-      <c r="ED4" s="54"/>
-      <c r="EE4" s="54"/>
-      <c r="EF4" s="54"/>
-      <c r="EG4" s="54"/>
-      <c r="EH4" s="54"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="64"/>
+      <c r="W4" s="64"/>
+      <c r="X4" s="64"/>
+      <c r="Y4" s="64"/>
+      <c r="Z4" s="64"/>
+      <c r="AA4" s="64"/>
+      <c r="AB4" s="64"/>
+      <c r="AC4" s="64"/>
+      <c r="AD4" s="64"/>
+      <c r="AE4" s="64"/>
+      <c r="AF4" s="64"/>
+      <c r="AG4" s="64"/>
+      <c r="AH4" s="64"/>
+      <c r="AI4" s="64"/>
+      <c r="AJ4" s="64"/>
+      <c r="AK4" s="64"/>
+      <c r="AL4" s="64"/>
+      <c r="AM4" s="64"/>
+      <c r="AN4" s="64"/>
+      <c r="AO4" s="64"/>
+      <c r="AP4" s="64"/>
+      <c r="AQ4" s="64"/>
+      <c r="AR4" s="64"/>
+      <c r="AS4" s="64"/>
+      <c r="AT4" s="64"/>
+      <c r="AU4" s="64"/>
+      <c r="AV4" s="64"/>
+      <c r="AW4" s="64"/>
+      <c r="AX4" s="64"/>
+      <c r="AY4" s="64"/>
+      <c r="AZ4" s="64"/>
+      <c r="BA4" s="64"/>
+      <c r="BB4" s="64"/>
+      <c r="BC4" s="64"/>
+      <c r="BD4" s="64"/>
+      <c r="BE4" s="64"/>
+      <c r="BF4" s="64"/>
+      <c r="BG4" s="64"/>
+      <c r="BH4" s="64"/>
+      <c r="BI4" s="64"/>
+      <c r="BJ4" s="64"/>
+      <c r="BK4" s="64"/>
+      <c r="BL4" s="64"/>
+      <c r="BM4" s="64"/>
+      <c r="BN4" s="64"/>
+      <c r="BO4" s="64"/>
+      <c r="BP4" s="64"/>
+      <c r="BQ4" s="64"/>
+      <c r="BR4" s="64"/>
+      <c r="BS4" s="64"/>
+      <c r="BT4" s="64"/>
+      <c r="BU4" s="64"/>
+      <c r="BV4" s="64"/>
+      <c r="BW4" s="64"/>
+      <c r="BX4" s="64"/>
+      <c r="BY4" s="64"/>
+      <c r="BZ4" s="64"/>
+      <c r="CA4" s="64"/>
+      <c r="CB4" s="64"/>
+      <c r="CC4" s="64"/>
+      <c r="CD4" s="64"/>
+      <c r="CE4" s="64"/>
+      <c r="CF4" s="64"/>
+      <c r="CG4" s="64"/>
+      <c r="CH4" s="64"/>
+      <c r="CI4" s="64"/>
+      <c r="CJ4" s="64"/>
+      <c r="CK4" s="64"/>
+      <c r="CL4" s="64"/>
+      <c r="CM4" s="64"/>
+      <c r="CN4" s="64"/>
+      <c r="CO4" s="64"/>
+      <c r="CP4" s="64"/>
+      <c r="CQ4" s="64"/>
+      <c r="CR4" s="64"/>
+      <c r="CS4" s="64"/>
+      <c r="CT4" s="64"/>
+      <c r="CU4" s="64"/>
+      <c r="CV4" s="64"/>
+      <c r="CW4" s="64"/>
+      <c r="CX4" s="64"/>
+      <c r="CY4" s="64"/>
+      <c r="CZ4" s="64"/>
+      <c r="DA4" s="64"/>
+      <c r="DB4" s="64"/>
+      <c r="DC4" s="64"/>
+      <c r="DD4" s="64"/>
+      <c r="DE4" s="64"/>
+      <c r="DF4" s="64"/>
+      <c r="DG4" s="64"/>
+      <c r="DH4" s="64"/>
+      <c r="DI4" s="64"/>
+      <c r="DJ4" s="64"/>
+      <c r="DK4" s="64"/>
+      <c r="DL4" s="64"/>
+      <c r="DM4" s="64"/>
+      <c r="DN4" s="64"/>
+      <c r="DO4" s="64"/>
+      <c r="DP4" s="64"/>
+      <c r="DQ4" s="64"/>
+      <c r="DR4" s="64"/>
+      <c r="DS4" s="64"/>
+      <c r="DT4" s="64"/>
+      <c r="DU4" s="64"/>
+      <c r="DV4" s="64"/>
+      <c r="DW4" s="64"/>
+      <c r="DX4" s="64"/>
+      <c r="DY4" s="64"/>
+      <c r="DZ4" s="64"/>
+      <c r="EA4" s="64"/>
+      <c r="EB4" s="64"/>
+      <c r="EC4" s="64"/>
+      <c r="ED4" s="64"/>
+      <c r="EE4" s="64"/>
+      <c r="EF4" s="64"/>
+      <c r="EG4" s="64"/>
+      <c r="EH4" s="64"/>
     </row>
     <row r="5" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="65" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="57" t="s">
+      <c r="C5" s="66" t="s">
         <v>78</v>
       </c>
       <c r="D5" s="9" t="s">
@@ -5981,9 +5981,9 @@
       </c>
     </row>
     <row r="6" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A6" s="55"/>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
+      <c r="A6" s="65"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
       <c r="D6" s="12" t="s">
         <v>80</v>
       </c>
@@ -6523,13 +6523,13 @@
       </c>
     </row>
     <row r="7" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="56" t="s">
+      <c r="B7" s="58" t="s">
         <v>82</v>
       </c>
-      <c r="C7" s="57" t="s">
+      <c r="C7" s="66" t="s">
         <v>83</v>
       </c>
       <c r="D7" s="9" t="s">
@@ -7071,9 +7071,9 @@
       </c>
     </row>
     <row r="8" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A8" s="55"/>
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
+      <c r="A8" s="65"/>
+      <c r="B8" s="65"/>
+      <c r="C8" s="65"/>
       <c r="D8" s="12" t="s">
         <v>80</v>
       </c>
@@ -7613,13 +7613,13 @@
       </c>
     </row>
     <row r="9" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="58" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="57" t="s">
+      <c r="C9" s="66" t="s">
         <v>86</v>
       </c>
       <c r="D9" s="9" t="s">
@@ -8161,9 +8161,9 @@
       </c>
     </row>
     <row r="10" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A10" s="55"/>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
+      <c r="A10" s="65"/>
+      <c r="B10" s="65"/>
+      <c r="C10" s="65"/>
       <c r="D10" s="12" t="s">
         <v>80</v>
       </c>
@@ -8703,155 +8703,155 @@
       </c>
     </row>
     <row r="11" spans="1:138" ht="15.75" customHeight="1">
-      <c r="A11" s="54" t="s">
+      <c r="A11" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="54"/>
-      <c r="L11" s="54"/>
-      <c r="M11" s="54"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="54"/>
-      <c r="P11" s="54"/>
-      <c r="Q11" s="54"/>
-      <c r="R11" s="54"/>
-      <c r="S11" s="54"/>
-      <c r="T11" s="54"/>
-      <c r="U11" s="54"/>
-      <c r="V11" s="54"/>
-      <c r="W11" s="54"/>
-      <c r="X11" s="54"/>
-      <c r="Y11" s="54"/>
-      <c r="Z11" s="54"/>
-      <c r="AA11" s="54"/>
-      <c r="AB11" s="54"/>
-      <c r="AC11" s="54"/>
-      <c r="AD11" s="54"/>
-      <c r="AE11" s="54"/>
-      <c r="AF11" s="54"/>
-      <c r="AG11" s="54"/>
-      <c r="AH11" s="54"/>
-      <c r="AI11" s="54"/>
-      <c r="AJ11" s="54"/>
-      <c r="AK11" s="54"/>
-      <c r="AL11" s="54"/>
-      <c r="AM11" s="54"/>
-      <c r="AN11" s="54"/>
-      <c r="AO11" s="54"/>
-      <c r="AP11" s="54"/>
-      <c r="AQ11" s="54"/>
-      <c r="AR11" s="54"/>
-      <c r="AS11" s="54"/>
-      <c r="AT11" s="54"/>
-      <c r="AU11" s="54"/>
-      <c r="AV11" s="54"/>
-      <c r="AW11" s="54"/>
-      <c r="AX11" s="54"/>
-      <c r="AY11" s="54"/>
-      <c r="AZ11" s="54"/>
-      <c r="BA11" s="54"/>
-      <c r="BB11" s="54"/>
-      <c r="BC11" s="54"/>
-      <c r="BD11" s="54"/>
-      <c r="BE11" s="54"/>
-      <c r="BF11" s="54"/>
-      <c r="BG11" s="54"/>
-      <c r="BH11" s="54"/>
-      <c r="BI11" s="54"/>
-      <c r="BJ11" s="54"/>
-      <c r="BK11" s="54"/>
-      <c r="BL11" s="54"/>
-      <c r="BM11" s="54"/>
-      <c r="BN11" s="54"/>
-      <c r="BO11" s="54"/>
-      <c r="BP11" s="54"/>
-      <c r="BQ11" s="54"/>
-      <c r="BR11" s="54"/>
-      <c r="BS11" s="54"/>
-      <c r="BT11" s="54"/>
-      <c r="BU11" s="54"/>
-      <c r="BV11" s="54"/>
-      <c r="BW11" s="54"/>
-      <c r="BX11" s="54"/>
-      <c r="BY11" s="54"/>
-      <c r="BZ11" s="54"/>
-      <c r="CA11" s="54"/>
-      <c r="CB11" s="54"/>
-      <c r="CC11" s="54"/>
-      <c r="CD11" s="54"/>
-      <c r="CE11" s="54"/>
-      <c r="CF11" s="54"/>
-      <c r="CG11" s="54"/>
-      <c r="CH11" s="54"/>
-      <c r="CI11" s="54"/>
-      <c r="CJ11" s="54"/>
-      <c r="CK11" s="54"/>
-      <c r="CL11" s="54"/>
-      <c r="CM11" s="54"/>
-      <c r="CN11" s="54"/>
-      <c r="CO11" s="54"/>
-      <c r="CP11" s="54"/>
-      <c r="CQ11" s="54"/>
-      <c r="CR11" s="54"/>
-      <c r="CS11" s="54"/>
-      <c r="CT11" s="54"/>
-      <c r="CU11" s="54"/>
-      <c r="CV11" s="54"/>
-      <c r="CW11" s="54"/>
-      <c r="CX11" s="54"/>
-      <c r="CY11" s="54"/>
-      <c r="CZ11" s="54"/>
-      <c r="DA11" s="54"/>
-      <c r="DB11" s="54"/>
-      <c r="DC11" s="54"/>
-      <c r="DD11" s="54"/>
-      <c r="DE11" s="54"/>
-      <c r="DF11" s="54"/>
-      <c r="DG11" s="54"/>
-      <c r="DH11" s="54"/>
-      <c r="DI11" s="54"/>
-      <c r="DJ11" s="54"/>
-      <c r="DK11" s="54"/>
-      <c r="DL11" s="54"/>
-      <c r="DM11" s="54"/>
-      <c r="DN11" s="54"/>
-      <c r="DO11" s="54"/>
-      <c r="DP11" s="54"/>
-      <c r="DQ11" s="54"/>
-      <c r="DR11" s="54"/>
-      <c r="DS11" s="54"/>
-      <c r="DT11" s="54"/>
-      <c r="DU11" s="54"/>
-      <c r="DV11" s="54"/>
-      <c r="DW11" s="54"/>
-      <c r="DX11" s="54"/>
-      <c r="DY11" s="54"/>
-      <c r="DZ11" s="54"/>
-      <c r="EA11" s="54"/>
-      <c r="EB11" s="54"/>
-      <c r="EC11" s="54"/>
-      <c r="ED11" s="54"/>
-      <c r="EE11" s="54"/>
-      <c r="EF11" s="54"/>
-      <c r="EG11" s="54"/>
-      <c r="EH11" s="54"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="64"/>
+      <c r="K11" s="64"/>
+      <c r="L11" s="64"/>
+      <c r="M11" s="64"/>
+      <c r="N11" s="64"/>
+      <c r="O11" s="64"/>
+      <c r="P11" s="64"/>
+      <c r="Q11" s="64"/>
+      <c r="R11" s="64"/>
+      <c r="S11" s="64"/>
+      <c r="T11" s="64"/>
+      <c r="U11" s="64"/>
+      <c r="V11" s="64"/>
+      <c r="W11" s="64"/>
+      <c r="X11" s="64"/>
+      <c r="Y11" s="64"/>
+      <c r="Z11" s="64"/>
+      <c r="AA11" s="64"/>
+      <c r="AB11" s="64"/>
+      <c r="AC11" s="64"/>
+      <c r="AD11" s="64"/>
+      <c r="AE11" s="64"/>
+      <c r="AF11" s="64"/>
+      <c r="AG11" s="64"/>
+      <c r="AH11" s="64"/>
+      <c r="AI11" s="64"/>
+      <c r="AJ11" s="64"/>
+      <c r="AK11" s="64"/>
+      <c r="AL11" s="64"/>
+      <c r="AM11" s="64"/>
+      <c r="AN11" s="64"/>
+      <c r="AO11" s="64"/>
+      <c r="AP11" s="64"/>
+      <c r="AQ11" s="64"/>
+      <c r="AR11" s="64"/>
+      <c r="AS11" s="64"/>
+      <c r="AT11" s="64"/>
+      <c r="AU11" s="64"/>
+      <c r="AV11" s="64"/>
+      <c r="AW11" s="64"/>
+      <c r="AX11" s="64"/>
+      <c r="AY11" s="64"/>
+      <c r="AZ11" s="64"/>
+      <c r="BA11" s="64"/>
+      <c r="BB11" s="64"/>
+      <c r="BC11" s="64"/>
+      <c r="BD11" s="64"/>
+      <c r="BE11" s="64"/>
+      <c r="BF11" s="64"/>
+      <c r="BG11" s="64"/>
+      <c r="BH11" s="64"/>
+      <c r="BI11" s="64"/>
+      <c r="BJ11" s="64"/>
+      <c r="BK11" s="64"/>
+      <c r="BL11" s="64"/>
+      <c r="BM11" s="64"/>
+      <c r="BN11" s="64"/>
+      <c r="BO11" s="64"/>
+      <c r="BP11" s="64"/>
+      <c r="BQ11" s="64"/>
+      <c r="BR11" s="64"/>
+      <c r="BS11" s="64"/>
+      <c r="BT11" s="64"/>
+      <c r="BU11" s="64"/>
+      <c r="BV11" s="64"/>
+      <c r="BW11" s="64"/>
+      <c r="BX11" s="64"/>
+      <c r="BY11" s="64"/>
+      <c r="BZ11" s="64"/>
+      <c r="CA11" s="64"/>
+      <c r="CB11" s="64"/>
+      <c r="CC11" s="64"/>
+      <c r="CD11" s="64"/>
+      <c r="CE11" s="64"/>
+      <c r="CF11" s="64"/>
+      <c r="CG11" s="64"/>
+      <c r="CH11" s="64"/>
+      <c r="CI11" s="64"/>
+      <c r="CJ11" s="64"/>
+      <c r="CK11" s="64"/>
+      <c r="CL11" s="64"/>
+      <c r="CM11" s="64"/>
+      <c r="CN11" s="64"/>
+      <c r="CO11" s="64"/>
+      <c r="CP11" s="64"/>
+      <c r="CQ11" s="64"/>
+      <c r="CR11" s="64"/>
+      <c r="CS11" s="64"/>
+      <c r="CT11" s="64"/>
+      <c r="CU11" s="64"/>
+      <c r="CV11" s="64"/>
+      <c r="CW11" s="64"/>
+      <c r="CX11" s="64"/>
+      <c r="CY11" s="64"/>
+      <c r="CZ11" s="64"/>
+      <c r="DA11" s="64"/>
+      <c r="DB11" s="64"/>
+      <c r="DC11" s="64"/>
+      <c r="DD11" s="64"/>
+      <c r="DE11" s="64"/>
+      <c r="DF11" s="64"/>
+      <c r="DG11" s="64"/>
+      <c r="DH11" s="64"/>
+      <c r="DI11" s="64"/>
+      <c r="DJ11" s="64"/>
+      <c r="DK11" s="64"/>
+      <c r="DL11" s="64"/>
+      <c r="DM11" s="64"/>
+      <c r="DN11" s="64"/>
+      <c r="DO11" s="64"/>
+      <c r="DP11" s="64"/>
+      <c r="DQ11" s="64"/>
+      <c r="DR11" s="64"/>
+      <c r="DS11" s="64"/>
+      <c r="DT11" s="64"/>
+      <c r="DU11" s="64"/>
+      <c r="DV11" s="64"/>
+      <c r="DW11" s="64"/>
+      <c r="DX11" s="64"/>
+      <c r="DY11" s="64"/>
+      <c r="DZ11" s="64"/>
+      <c r="EA11" s="64"/>
+      <c r="EB11" s="64"/>
+      <c r="EC11" s="64"/>
+      <c r="ED11" s="64"/>
+      <c r="EE11" s="64"/>
+      <c r="EF11" s="64"/>
+      <c r="EG11" s="64"/>
+      <c r="EH11" s="64"/>
     </row>
     <row r="12" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="56" t="s">
+      <c r="B12" s="58" t="s">
         <v>89</v>
       </c>
-      <c r="C12" s="57" t="s">
+      <c r="C12" s="66" t="s">
         <v>90</v>
       </c>
       <c r="D12" s="9" t="s">
@@ -9393,9 +9393,9 @@
       </c>
     </row>
     <row r="13" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A13" s="55"/>
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
+      <c r="A13" s="65"/>
+      <c r="B13" s="65"/>
+      <c r="C13" s="65"/>
       <c r="D13" s="12" t="s">
         <v>80</v>
       </c>
@@ -9935,13 +9935,13 @@
       </c>
     </row>
     <row r="14" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A14" s="55" t="s">
+      <c r="A14" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="B14" s="56" t="s">
+      <c r="B14" s="58" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="57" t="s">
+      <c r="C14" s="66" t="s">
         <v>90</v>
       </c>
       <c r="D14" s="9" t="s">
@@ -10483,9 +10483,9 @@
       </c>
     </row>
     <row r="15" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A15" s="55"/>
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
+      <c r="A15" s="65"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="65"/>
       <c r="D15" s="12" t="s">
         <v>80</v>
       </c>
@@ -11025,13 +11025,13 @@
       </c>
     </row>
     <row r="16" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A16" s="55" t="s">
+      <c r="A16" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="B16" s="56" t="s">
+      <c r="B16" s="58" t="s">
         <v>94</v>
       </c>
-      <c r="C16" s="57" t="s">
+      <c r="C16" s="66" t="s">
         <v>95</v>
       </c>
       <c r="D16" s="9" t="s">
@@ -11573,9 +11573,9 @@
       </c>
     </row>
     <row r="17" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A17" s="55"/>
-      <c r="B17" s="55"/>
-      <c r="C17" s="55"/>
+      <c r="A17" s="65"/>
+      <c r="B17" s="65"/>
+      <c r="C17" s="65"/>
       <c r="D17" s="12" t="s">
         <v>80</v>
       </c>
@@ -12115,13 +12115,13 @@
       </c>
     </row>
     <row r="18" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A18" s="55" t="s">
+      <c r="A18" s="65" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="56" t="s">
+      <c r="B18" s="58" t="s">
         <v>97</v>
       </c>
-      <c r="C18" s="57" t="s">
+      <c r="C18" s="66" t="s">
         <v>95</v>
       </c>
       <c r="D18" s="9" t="s">
@@ -12663,9 +12663,9 @@
       </c>
     </row>
     <row r="19" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A19" s="55"/>
-      <c r="B19" s="55"/>
-      <c r="C19" s="55"/>
+      <c r="A19" s="65"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="65"/>
       <c r="D19" s="12" t="s">
         <v>80</v>
       </c>
@@ -13205,155 +13205,155 @@
       </c>
     </row>
     <row r="20" spans="1:138" ht="15.75" customHeight="1">
-      <c r="A20" s="54" t="s">
+      <c r="A20" s="64" t="s">
         <v>98</v>
       </c>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="54"/>
-      <c r="J20" s="54"/>
-      <c r="K20" s="54"/>
-      <c r="L20" s="54"/>
-      <c r="M20" s="54"/>
-      <c r="N20" s="54"/>
-      <c r="O20" s="54"/>
-      <c r="P20" s="54"/>
-      <c r="Q20" s="54"/>
-      <c r="R20" s="54"/>
-      <c r="S20" s="54"/>
-      <c r="T20" s="54"/>
-      <c r="U20" s="54"/>
-      <c r="V20" s="54"/>
-      <c r="W20" s="54"/>
-      <c r="X20" s="54"/>
-      <c r="Y20" s="54"/>
-      <c r="Z20" s="54"/>
-      <c r="AA20" s="54"/>
-      <c r="AB20" s="54"/>
-      <c r="AC20" s="54"/>
-      <c r="AD20" s="54"/>
-      <c r="AE20" s="54"/>
-      <c r="AF20" s="54"/>
-      <c r="AG20" s="54"/>
-      <c r="AH20" s="54"/>
-      <c r="AI20" s="54"/>
-      <c r="AJ20" s="54"/>
-      <c r="AK20" s="54"/>
-      <c r="AL20" s="54"/>
-      <c r="AM20" s="54"/>
-      <c r="AN20" s="54"/>
-      <c r="AO20" s="54"/>
-      <c r="AP20" s="54"/>
-      <c r="AQ20" s="54"/>
-      <c r="AR20" s="54"/>
-      <c r="AS20" s="54"/>
-      <c r="AT20" s="54"/>
-      <c r="AU20" s="54"/>
-      <c r="AV20" s="54"/>
-      <c r="AW20" s="54"/>
-      <c r="AX20" s="54"/>
-      <c r="AY20" s="54"/>
-      <c r="AZ20" s="54"/>
-      <c r="BA20" s="54"/>
-      <c r="BB20" s="54"/>
-      <c r="BC20" s="54"/>
-      <c r="BD20" s="54"/>
-      <c r="BE20" s="54"/>
-      <c r="BF20" s="54"/>
-      <c r="BG20" s="54"/>
-      <c r="BH20" s="54"/>
-      <c r="BI20" s="54"/>
-      <c r="BJ20" s="54"/>
-      <c r="BK20" s="54"/>
-      <c r="BL20" s="54"/>
-      <c r="BM20" s="54"/>
-      <c r="BN20" s="54"/>
-      <c r="BO20" s="54"/>
-      <c r="BP20" s="54"/>
-      <c r="BQ20" s="54"/>
-      <c r="BR20" s="54"/>
-      <c r="BS20" s="54"/>
-      <c r="BT20" s="54"/>
-      <c r="BU20" s="54"/>
-      <c r="BV20" s="54"/>
-      <c r="BW20" s="54"/>
-      <c r="BX20" s="54"/>
-      <c r="BY20" s="54"/>
-      <c r="BZ20" s="54"/>
-      <c r="CA20" s="54"/>
-      <c r="CB20" s="54"/>
-      <c r="CC20" s="54"/>
-      <c r="CD20" s="54"/>
-      <c r="CE20" s="54"/>
-      <c r="CF20" s="54"/>
-      <c r="CG20" s="54"/>
-      <c r="CH20" s="54"/>
-      <c r="CI20" s="54"/>
-      <c r="CJ20" s="54"/>
-      <c r="CK20" s="54"/>
-      <c r="CL20" s="54"/>
-      <c r="CM20" s="54"/>
-      <c r="CN20" s="54"/>
-      <c r="CO20" s="54"/>
-      <c r="CP20" s="54"/>
-      <c r="CQ20" s="54"/>
-      <c r="CR20" s="54"/>
-      <c r="CS20" s="54"/>
-      <c r="CT20" s="54"/>
-      <c r="CU20" s="54"/>
-      <c r="CV20" s="54"/>
-      <c r="CW20" s="54"/>
-      <c r="CX20" s="54"/>
-      <c r="CY20" s="54"/>
-      <c r="CZ20" s="54"/>
-      <c r="DA20" s="54"/>
-      <c r="DB20" s="54"/>
-      <c r="DC20" s="54"/>
-      <c r="DD20" s="54"/>
-      <c r="DE20" s="54"/>
-      <c r="DF20" s="54"/>
-      <c r="DG20" s="54"/>
-      <c r="DH20" s="54"/>
-      <c r="DI20" s="54"/>
-      <c r="DJ20" s="54"/>
-      <c r="DK20" s="54"/>
-      <c r="DL20" s="54"/>
-      <c r="DM20" s="54"/>
-      <c r="DN20" s="54"/>
-      <c r="DO20" s="54"/>
-      <c r="DP20" s="54"/>
-      <c r="DQ20" s="54"/>
-      <c r="DR20" s="54"/>
-      <c r="DS20" s="54"/>
-      <c r="DT20" s="54"/>
-      <c r="DU20" s="54"/>
-      <c r="DV20" s="54"/>
-      <c r="DW20" s="54"/>
-      <c r="DX20" s="54"/>
-      <c r="DY20" s="54"/>
-      <c r="DZ20" s="54"/>
-      <c r="EA20" s="54"/>
-      <c r="EB20" s="54"/>
-      <c r="EC20" s="54"/>
-      <c r="ED20" s="54"/>
-      <c r="EE20" s="54"/>
-      <c r="EF20" s="54"/>
-      <c r="EG20" s="54"/>
-      <c r="EH20" s="54"/>
+      <c r="B20" s="64"/>
+      <c r="C20" s="64"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="64"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="64"/>
+      <c r="K20" s="64"/>
+      <c r="L20" s="64"/>
+      <c r="M20" s="64"/>
+      <c r="N20" s="64"/>
+      <c r="O20" s="64"/>
+      <c r="P20" s="64"/>
+      <c r="Q20" s="64"/>
+      <c r="R20" s="64"/>
+      <c r="S20" s="64"/>
+      <c r="T20" s="64"/>
+      <c r="U20" s="64"/>
+      <c r="V20" s="64"/>
+      <c r="W20" s="64"/>
+      <c r="X20" s="64"/>
+      <c r="Y20" s="64"/>
+      <c r="Z20" s="64"/>
+      <c r="AA20" s="64"/>
+      <c r="AB20" s="64"/>
+      <c r="AC20" s="64"/>
+      <c r="AD20" s="64"/>
+      <c r="AE20" s="64"/>
+      <c r="AF20" s="64"/>
+      <c r="AG20" s="64"/>
+      <c r="AH20" s="64"/>
+      <c r="AI20" s="64"/>
+      <c r="AJ20" s="64"/>
+      <c r="AK20" s="64"/>
+      <c r="AL20" s="64"/>
+      <c r="AM20" s="64"/>
+      <c r="AN20" s="64"/>
+      <c r="AO20" s="64"/>
+      <c r="AP20" s="64"/>
+      <c r="AQ20" s="64"/>
+      <c r="AR20" s="64"/>
+      <c r="AS20" s="64"/>
+      <c r="AT20" s="64"/>
+      <c r="AU20" s="64"/>
+      <c r="AV20" s="64"/>
+      <c r="AW20" s="64"/>
+      <c r="AX20" s="64"/>
+      <c r="AY20" s="64"/>
+      <c r="AZ20" s="64"/>
+      <c r="BA20" s="64"/>
+      <c r="BB20" s="64"/>
+      <c r="BC20" s="64"/>
+      <c r="BD20" s="64"/>
+      <c r="BE20" s="64"/>
+      <c r="BF20" s="64"/>
+      <c r="BG20" s="64"/>
+      <c r="BH20" s="64"/>
+      <c r="BI20" s="64"/>
+      <c r="BJ20" s="64"/>
+      <c r="BK20" s="64"/>
+      <c r="BL20" s="64"/>
+      <c r="BM20" s="64"/>
+      <c r="BN20" s="64"/>
+      <c r="BO20" s="64"/>
+      <c r="BP20" s="64"/>
+      <c r="BQ20" s="64"/>
+      <c r="BR20" s="64"/>
+      <c r="BS20" s="64"/>
+      <c r="BT20" s="64"/>
+      <c r="BU20" s="64"/>
+      <c r="BV20" s="64"/>
+      <c r="BW20" s="64"/>
+      <c r="BX20" s="64"/>
+      <c r="BY20" s="64"/>
+      <c r="BZ20" s="64"/>
+      <c r="CA20" s="64"/>
+      <c r="CB20" s="64"/>
+      <c r="CC20" s="64"/>
+      <c r="CD20" s="64"/>
+      <c r="CE20" s="64"/>
+      <c r="CF20" s="64"/>
+      <c r="CG20" s="64"/>
+      <c r="CH20" s="64"/>
+      <c r="CI20" s="64"/>
+      <c r="CJ20" s="64"/>
+      <c r="CK20" s="64"/>
+      <c r="CL20" s="64"/>
+      <c r="CM20" s="64"/>
+      <c r="CN20" s="64"/>
+      <c r="CO20" s="64"/>
+      <c r="CP20" s="64"/>
+      <c r="CQ20" s="64"/>
+      <c r="CR20" s="64"/>
+      <c r="CS20" s="64"/>
+      <c r="CT20" s="64"/>
+      <c r="CU20" s="64"/>
+      <c r="CV20" s="64"/>
+      <c r="CW20" s="64"/>
+      <c r="CX20" s="64"/>
+      <c r="CY20" s="64"/>
+      <c r="CZ20" s="64"/>
+      <c r="DA20" s="64"/>
+      <c r="DB20" s="64"/>
+      <c r="DC20" s="64"/>
+      <c r="DD20" s="64"/>
+      <c r="DE20" s="64"/>
+      <c r="DF20" s="64"/>
+      <c r="DG20" s="64"/>
+      <c r="DH20" s="64"/>
+      <c r="DI20" s="64"/>
+      <c r="DJ20" s="64"/>
+      <c r="DK20" s="64"/>
+      <c r="DL20" s="64"/>
+      <c r="DM20" s="64"/>
+      <c r="DN20" s="64"/>
+      <c r="DO20" s="64"/>
+      <c r="DP20" s="64"/>
+      <c r="DQ20" s="64"/>
+      <c r="DR20" s="64"/>
+      <c r="DS20" s="64"/>
+      <c r="DT20" s="64"/>
+      <c r="DU20" s="64"/>
+      <c r="DV20" s="64"/>
+      <c r="DW20" s="64"/>
+      <c r="DX20" s="64"/>
+      <c r="DY20" s="64"/>
+      <c r="DZ20" s="64"/>
+      <c r="EA20" s="64"/>
+      <c r="EB20" s="64"/>
+      <c r="EC20" s="64"/>
+      <c r="ED20" s="64"/>
+      <c r="EE20" s="64"/>
+      <c r="EF20" s="64"/>
+      <c r="EG20" s="64"/>
+      <c r="EH20" s="64"/>
     </row>
     <row r="21" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A21" s="55" t="s">
+      <c r="A21" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="B21" s="56" t="s">
+      <c r="B21" s="58" t="s">
         <v>100</v>
       </c>
-      <c r="C21" s="57" t="s">
+      <c r="C21" s="66" t="s">
         <v>101</v>
       </c>
       <c r="D21" s="9" t="s">
@@ -13895,9 +13895,9 @@
       </c>
     </row>
     <row r="22" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A22" s="55"/>
-      <c r="B22" s="55"/>
-      <c r="C22" s="57"/>
+      <c r="A22" s="65"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="66"/>
       <c r="D22" s="12" t="s">
         <v>80</v>
       </c>
@@ -14437,13 +14437,13 @@
       </c>
     </row>
     <row r="23" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A23" s="55" t="s">
+      <c r="A23" s="65" t="s">
         <v>102</v>
       </c>
-      <c r="B23" s="56" t="s">
+      <c r="B23" s="58" t="s">
         <v>103</v>
       </c>
-      <c r="C23" s="57" t="s">
+      <c r="C23" s="66" t="s">
         <v>101</v>
       </c>
       <c r="D23" s="9" t="s">
@@ -14985,9 +14985,9 @@
       </c>
     </row>
     <row r="24" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A24" s="55"/>
-      <c r="B24" s="55"/>
-      <c r="C24" s="55"/>
+      <c r="A24" s="65"/>
+      <c r="B24" s="65"/>
+      <c r="C24" s="65"/>
       <c r="D24" s="12" t="s">
         <v>80</v>
       </c>
@@ -15527,13 +15527,13 @@
       </c>
     </row>
     <row r="25" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A25" s="55" t="s">
+      <c r="A25" s="65" t="s">
         <v>104</v>
       </c>
-      <c r="B25" s="56" t="s">
+      <c r="B25" s="58" t="s">
         <v>105</v>
       </c>
-      <c r="C25" s="57" t="s">
+      <c r="C25" s="66" t="s">
         <v>86</v>
       </c>
       <c r="D25" s="9" t="s">
@@ -16075,9 +16075,9 @@
       </c>
     </row>
     <row r="26" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A26" s="55"/>
-      <c r="B26" s="55"/>
-      <c r="C26" s="55"/>
+      <c r="A26" s="65"/>
+      <c r="B26" s="65"/>
+      <c r="C26" s="65"/>
       <c r="D26" s="12" t="s">
         <v>80</v>
       </c>
@@ -16617,13 +16617,13 @@
       </c>
     </row>
     <row r="27" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A27" s="55" t="s">
+      <c r="A27" s="65" t="s">
         <v>106</v>
       </c>
-      <c r="B27" s="56" t="s">
+      <c r="B27" s="58" t="s">
         <v>107</v>
       </c>
-      <c r="C27" s="57" t="s">
+      <c r="C27" s="66" t="s">
         <v>101</v>
       </c>
       <c r="D27" s="9" t="s">
@@ -17165,9 +17165,9 @@
       </c>
     </row>
     <row r="28" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A28" s="55"/>
-      <c r="B28" s="55"/>
-      <c r="C28" s="55"/>
+      <c r="A28" s="65"/>
+      <c r="B28" s="65"/>
+      <c r="C28" s="65"/>
       <c r="D28" s="12" t="s">
         <v>80</v>
       </c>
@@ -17707,13 +17707,13 @@
       </c>
     </row>
     <row r="29" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A29" s="55" t="s">
+      <c r="A29" s="65" t="s">
         <v>108</v>
       </c>
-      <c r="B29" s="56" t="s">
+      <c r="B29" s="58" t="s">
         <v>109</v>
       </c>
-      <c r="C29" s="57" t="s">
+      <c r="C29" s="66" t="s">
         <v>86</v>
       </c>
       <c r="D29" s="9" t="s">
@@ -18255,9 +18255,9 @@
       </c>
     </row>
     <row r="30" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A30" s="55"/>
-      <c r="B30" s="55"/>
-      <c r="C30" s="55"/>
+      <c r="A30" s="65"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="65"/>
       <c r="D30" s="12" t="s">
         <v>80</v>
       </c>
@@ -18793,13 +18793,13 @@
       </c>
     </row>
     <row r="31" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A31" s="55" t="s">
+      <c r="A31" s="65" t="s">
         <v>110</v>
       </c>
-      <c r="B31" s="56" t="s">
+      <c r="B31" s="58" t="s">
         <v>111</v>
       </c>
-      <c r="C31" s="57" t="s">
+      <c r="C31" s="66" t="s">
         <v>78</v>
       </c>
       <c r="D31" s="9" t="s">
@@ -19341,9 +19341,9 @@
       </c>
     </row>
     <row r="32" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A32" s="55"/>
-      <c r="B32" s="55"/>
-      <c r="C32" s="55"/>
+      <c r="A32" s="65"/>
+      <c r="B32" s="65"/>
+      <c r="C32" s="65"/>
       <c r="D32" s="12" t="s">
         <v>80</v>
       </c>
@@ -19883,13 +19883,13 @@
       </c>
     </row>
     <row r="33" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A33" s="55" t="s">
+      <c r="A33" s="65" t="s">
         <v>112</v>
       </c>
-      <c r="B33" s="56" t="s">
+      <c r="B33" s="58" t="s">
         <v>113</v>
       </c>
-      <c r="C33" s="57" t="s">
+      <c r="C33" s="66" t="s">
         <v>101</v>
       </c>
       <c r="D33" s="9" t="s">
@@ -20431,9 +20431,9 @@
       </c>
     </row>
     <row r="34" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A34" s="55"/>
-      <c r="B34" s="55"/>
-      <c r="C34" s="55"/>
+      <c r="A34" s="65"/>
+      <c r="B34" s="65"/>
+      <c r="C34" s="65"/>
       <c r="D34" s="12" t="s">
         <v>80</v>
       </c>
@@ -20973,155 +20973,155 @@
       </c>
     </row>
     <row r="35" spans="1:138" ht="15.75" customHeight="1">
-      <c r="A35" s="54" t="s">
+      <c r="A35" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="B35" s="54"/>
-      <c r="C35" s="54"/>
-      <c r="D35" s="54"/>
-      <c r="E35" s="54"/>
-      <c r="F35" s="54"/>
-      <c r="G35" s="54"/>
-      <c r="H35" s="54"/>
-      <c r="I35" s="54"/>
-      <c r="J35" s="54"/>
-      <c r="K35" s="54"/>
-      <c r="L35" s="54"/>
-      <c r="M35" s="54"/>
-      <c r="N35" s="54"/>
-      <c r="O35" s="54"/>
-      <c r="P35" s="54"/>
-      <c r="Q35" s="54"/>
-      <c r="R35" s="54"/>
-      <c r="S35" s="54"/>
-      <c r="T35" s="54"/>
-      <c r="U35" s="54"/>
-      <c r="V35" s="54"/>
-      <c r="W35" s="54"/>
-      <c r="X35" s="54"/>
-      <c r="Y35" s="54"/>
-      <c r="Z35" s="54"/>
-      <c r="AA35" s="54"/>
-      <c r="AB35" s="54"/>
-      <c r="AC35" s="54"/>
-      <c r="AD35" s="54"/>
-      <c r="AE35" s="54"/>
-      <c r="AF35" s="54"/>
-      <c r="AG35" s="54"/>
-      <c r="AH35" s="54"/>
-      <c r="AI35" s="54"/>
-      <c r="AJ35" s="54"/>
-      <c r="AK35" s="54"/>
-      <c r="AL35" s="54"/>
-      <c r="AM35" s="54"/>
-      <c r="AN35" s="54"/>
-      <c r="AO35" s="54"/>
-      <c r="AP35" s="54"/>
-      <c r="AQ35" s="54"/>
-      <c r="AR35" s="54"/>
-      <c r="AS35" s="54"/>
-      <c r="AT35" s="54"/>
-      <c r="AU35" s="54"/>
-      <c r="AV35" s="54"/>
-      <c r="AW35" s="54"/>
-      <c r="AX35" s="54"/>
-      <c r="AY35" s="54"/>
-      <c r="AZ35" s="54"/>
-      <c r="BA35" s="54"/>
-      <c r="BB35" s="54"/>
-      <c r="BC35" s="54"/>
-      <c r="BD35" s="54"/>
-      <c r="BE35" s="54"/>
-      <c r="BF35" s="54"/>
-      <c r="BG35" s="54"/>
-      <c r="BH35" s="54"/>
-      <c r="BI35" s="54"/>
-      <c r="BJ35" s="54"/>
-      <c r="BK35" s="54"/>
-      <c r="BL35" s="54"/>
-      <c r="BM35" s="54"/>
-      <c r="BN35" s="54"/>
-      <c r="BO35" s="54"/>
-      <c r="BP35" s="54"/>
-      <c r="BQ35" s="54"/>
-      <c r="BR35" s="54"/>
-      <c r="BS35" s="54"/>
-      <c r="BT35" s="54"/>
-      <c r="BU35" s="54"/>
-      <c r="BV35" s="54"/>
-      <c r="BW35" s="54"/>
-      <c r="BX35" s="54"/>
-      <c r="BY35" s="54"/>
-      <c r="BZ35" s="54"/>
-      <c r="CA35" s="54"/>
-      <c r="CB35" s="54"/>
-      <c r="CC35" s="54"/>
-      <c r="CD35" s="54"/>
-      <c r="CE35" s="54"/>
-      <c r="CF35" s="54"/>
-      <c r="CG35" s="54"/>
-      <c r="CH35" s="54"/>
-      <c r="CI35" s="54"/>
-      <c r="CJ35" s="54"/>
-      <c r="CK35" s="54"/>
-      <c r="CL35" s="54"/>
-      <c r="CM35" s="54"/>
-      <c r="CN35" s="54"/>
-      <c r="CO35" s="54"/>
-      <c r="CP35" s="54"/>
-      <c r="CQ35" s="54"/>
-      <c r="CR35" s="54"/>
-      <c r="CS35" s="54"/>
-      <c r="CT35" s="54"/>
-      <c r="CU35" s="54"/>
-      <c r="CV35" s="54"/>
-      <c r="CW35" s="54"/>
-      <c r="CX35" s="54"/>
-      <c r="CY35" s="54"/>
-      <c r="CZ35" s="54"/>
-      <c r="DA35" s="54"/>
-      <c r="DB35" s="54"/>
-      <c r="DC35" s="54"/>
-      <c r="DD35" s="54"/>
-      <c r="DE35" s="54"/>
-      <c r="DF35" s="54"/>
-      <c r="DG35" s="54"/>
-      <c r="DH35" s="54"/>
-      <c r="DI35" s="54"/>
-      <c r="DJ35" s="54"/>
-      <c r="DK35" s="54"/>
-      <c r="DL35" s="54"/>
-      <c r="DM35" s="54"/>
-      <c r="DN35" s="54"/>
-      <c r="DO35" s="54"/>
-      <c r="DP35" s="54"/>
-      <c r="DQ35" s="54"/>
-      <c r="DR35" s="54"/>
-      <c r="DS35" s="54"/>
-      <c r="DT35" s="54"/>
-      <c r="DU35" s="54"/>
-      <c r="DV35" s="54"/>
-      <c r="DW35" s="54"/>
-      <c r="DX35" s="54"/>
-      <c r="DY35" s="54"/>
-      <c r="DZ35" s="54"/>
-      <c r="EA35" s="54"/>
-      <c r="EB35" s="54"/>
-      <c r="EC35" s="54"/>
-      <c r="ED35" s="54"/>
-      <c r="EE35" s="54"/>
-      <c r="EF35" s="54"/>
-      <c r="EG35" s="54"/>
-      <c r="EH35" s="54"/>
+      <c r="B35" s="64"/>
+      <c r="C35" s="64"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="64"/>
+      <c r="F35" s="64"/>
+      <c r="G35" s="64"/>
+      <c r="H35" s="64"/>
+      <c r="I35" s="64"/>
+      <c r="J35" s="64"/>
+      <c r="K35" s="64"/>
+      <c r="L35" s="64"/>
+      <c r="M35" s="64"/>
+      <c r="N35" s="64"/>
+      <c r="O35" s="64"/>
+      <c r="P35" s="64"/>
+      <c r="Q35" s="64"/>
+      <c r="R35" s="64"/>
+      <c r="S35" s="64"/>
+      <c r="T35" s="64"/>
+      <c r="U35" s="64"/>
+      <c r="V35" s="64"/>
+      <c r="W35" s="64"/>
+      <c r="X35" s="64"/>
+      <c r="Y35" s="64"/>
+      <c r="Z35" s="64"/>
+      <c r="AA35" s="64"/>
+      <c r="AB35" s="64"/>
+      <c r="AC35" s="64"/>
+      <c r="AD35" s="64"/>
+      <c r="AE35" s="64"/>
+      <c r="AF35" s="64"/>
+      <c r="AG35" s="64"/>
+      <c r="AH35" s="64"/>
+      <c r="AI35" s="64"/>
+      <c r="AJ35" s="64"/>
+      <c r="AK35" s="64"/>
+      <c r="AL35" s="64"/>
+      <c r="AM35" s="64"/>
+      <c r="AN35" s="64"/>
+      <c r="AO35" s="64"/>
+      <c r="AP35" s="64"/>
+      <c r="AQ35" s="64"/>
+      <c r="AR35" s="64"/>
+      <c r="AS35" s="64"/>
+      <c r="AT35" s="64"/>
+      <c r="AU35" s="64"/>
+      <c r="AV35" s="64"/>
+      <c r="AW35" s="64"/>
+      <c r="AX35" s="64"/>
+      <c r="AY35" s="64"/>
+      <c r="AZ35" s="64"/>
+      <c r="BA35" s="64"/>
+      <c r="BB35" s="64"/>
+      <c r="BC35" s="64"/>
+      <c r="BD35" s="64"/>
+      <c r="BE35" s="64"/>
+      <c r="BF35" s="64"/>
+      <c r="BG35" s="64"/>
+      <c r="BH35" s="64"/>
+      <c r="BI35" s="64"/>
+      <c r="BJ35" s="64"/>
+      <c r="BK35" s="64"/>
+      <c r="BL35" s="64"/>
+      <c r="BM35" s="64"/>
+      <c r="BN35" s="64"/>
+      <c r="BO35" s="64"/>
+      <c r="BP35" s="64"/>
+      <c r="BQ35" s="64"/>
+      <c r="BR35" s="64"/>
+      <c r="BS35" s="64"/>
+      <c r="BT35" s="64"/>
+      <c r="BU35" s="64"/>
+      <c r="BV35" s="64"/>
+      <c r="BW35" s="64"/>
+      <c r="BX35" s="64"/>
+      <c r="BY35" s="64"/>
+      <c r="BZ35" s="64"/>
+      <c r="CA35" s="64"/>
+      <c r="CB35" s="64"/>
+      <c r="CC35" s="64"/>
+      <c r="CD35" s="64"/>
+      <c r="CE35" s="64"/>
+      <c r="CF35" s="64"/>
+      <c r="CG35" s="64"/>
+      <c r="CH35" s="64"/>
+      <c r="CI35" s="64"/>
+      <c r="CJ35" s="64"/>
+      <c r="CK35" s="64"/>
+      <c r="CL35" s="64"/>
+      <c r="CM35" s="64"/>
+      <c r="CN35" s="64"/>
+      <c r="CO35" s="64"/>
+      <c r="CP35" s="64"/>
+      <c r="CQ35" s="64"/>
+      <c r="CR35" s="64"/>
+      <c r="CS35" s="64"/>
+      <c r="CT35" s="64"/>
+      <c r="CU35" s="64"/>
+      <c r="CV35" s="64"/>
+      <c r="CW35" s="64"/>
+      <c r="CX35" s="64"/>
+      <c r="CY35" s="64"/>
+      <c r="CZ35" s="64"/>
+      <c r="DA35" s="64"/>
+      <c r="DB35" s="64"/>
+      <c r="DC35" s="64"/>
+      <c r="DD35" s="64"/>
+      <c r="DE35" s="64"/>
+      <c r="DF35" s="64"/>
+      <c r="DG35" s="64"/>
+      <c r="DH35" s="64"/>
+      <c r="DI35" s="64"/>
+      <c r="DJ35" s="64"/>
+      <c r="DK35" s="64"/>
+      <c r="DL35" s="64"/>
+      <c r="DM35" s="64"/>
+      <c r="DN35" s="64"/>
+      <c r="DO35" s="64"/>
+      <c r="DP35" s="64"/>
+      <c r="DQ35" s="64"/>
+      <c r="DR35" s="64"/>
+      <c r="DS35" s="64"/>
+      <c r="DT35" s="64"/>
+      <c r="DU35" s="64"/>
+      <c r="DV35" s="64"/>
+      <c r="DW35" s="64"/>
+      <c r="DX35" s="64"/>
+      <c r="DY35" s="64"/>
+      <c r="DZ35" s="64"/>
+      <c r="EA35" s="64"/>
+      <c r="EB35" s="64"/>
+      <c r="EC35" s="64"/>
+      <c r="ED35" s="64"/>
+      <c r="EE35" s="64"/>
+      <c r="EF35" s="64"/>
+      <c r="EG35" s="64"/>
+      <c r="EH35" s="64"/>
     </row>
     <row r="36" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A36" s="55" t="s">
+      <c r="A36" s="65" t="s">
         <v>115</v>
       </c>
-      <c r="B36" s="56" t="s">
+      <c r="B36" s="58" t="s">
         <v>116</v>
       </c>
-      <c r="C36" s="57" t="s">
+      <c r="C36" s="66" t="s">
         <v>90</v>
       </c>
       <c r="D36" s="9" t="s">
@@ -21663,9 +21663,9 @@
       </c>
     </row>
     <row r="37" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A37" s="55"/>
-      <c r="B37" s="55"/>
-      <c r="C37" s="55"/>
+      <c r="A37" s="65"/>
+      <c r="B37" s="65"/>
+      <c r="C37" s="65"/>
       <c r="D37" s="12" t="s">
         <v>80</v>
       </c>
@@ -22205,13 +22205,13 @@
       </c>
     </row>
     <row r="38" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A38" s="55" t="s">
+      <c r="A38" s="65" t="s">
         <v>117</v>
       </c>
-      <c r="B38" s="56" t="s">
+      <c r="B38" s="58" t="s">
         <v>118</v>
       </c>
-      <c r="C38" s="57" t="s">
+      <c r="C38" s="66" t="s">
         <v>90</v>
       </c>
       <c r="D38" s="9" t="s">
@@ -22753,9 +22753,9 @@
       </c>
     </row>
     <row r="39" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A39" s="55"/>
-      <c r="B39" s="55"/>
-      <c r="C39" s="55"/>
+      <c r="A39" s="65"/>
+      <c r="B39" s="65"/>
+      <c r="C39" s="65"/>
       <c r="D39" s="12" t="s">
         <v>80</v>
       </c>
@@ -23295,13 +23295,13 @@
       </c>
     </row>
     <row r="40" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A40" s="55" t="s">
+      <c r="A40" s="65" t="s">
         <v>119</v>
       </c>
-      <c r="B40" s="56" t="s">
+      <c r="B40" s="58" t="s">
         <v>120</v>
       </c>
-      <c r="C40" s="57" t="s">
+      <c r="C40" s="66" t="s">
         <v>90</v>
       </c>
       <c r="D40" s="9" t="s">
@@ -23843,9 +23843,9 @@
       </c>
     </row>
     <row r="41" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A41" s="55"/>
-      <c r="B41" s="55"/>
-      <c r="C41" s="55"/>
+      <c r="A41" s="65"/>
+      <c r="B41" s="65"/>
+      <c r="C41" s="65"/>
       <c r="D41" s="12" t="s">
         <v>80</v>
       </c>
@@ -24385,155 +24385,155 @@
       </c>
     </row>
     <row r="42" spans="1:138" ht="15.75" customHeight="1">
-      <c r="A42" s="54" t="s">
+      <c r="A42" s="64" t="s">
         <v>121</v>
       </c>
-      <c r="B42" s="54"/>
-      <c r="C42" s="54"/>
-      <c r="D42" s="54"/>
-      <c r="E42" s="54"/>
-      <c r="F42" s="54"/>
-      <c r="G42" s="54"/>
-      <c r="H42" s="54"/>
-      <c r="I42" s="54"/>
-      <c r="J42" s="54"/>
-      <c r="K42" s="54"/>
-      <c r="L42" s="54"/>
-      <c r="M42" s="54"/>
-      <c r="N42" s="54"/>
-      <c r="O42" s="54"/>
-      <c r="P42" s="54"/>
-      <c r="Q42" s="54"/>
-      <c r="R42" s="54"/>
-      <c r="S42" s="54"/>
-      <c r="T42" s="54"/>
-      <c r="U42" s="54"/>
-      <c r="V42" s="54"/>
-      <c r="W42" s="54"/>
-      <c r="X42" s="54"/>
-      <c r="Y42" s="54"/>
-      <c r="Z42" s="54"/>
-      <c r="AA42" s="54"/>
-      <c r="AB42" s="54"/>
-      <c r="AC42" s="54"/>
-      <c r="AD42" s="54"/>
-      <c r="AE42" s="54"/>
-      <c r="AF42" s="54"/>
-      <c r="AG42" s="54"/>
-      <c r="AH42" s="54"/>
-      <c r="AI42" s="54"/>
-      <c r="AJ42" s="54"/>
-      <c r="AK42" s="54"/>
-      <c r="AL42" s="54"/>
-      <c r="AM42" s="54"/>
-      <c r="AN42" s="54"/>
-      <c r="AO42" s="54"/>
-      <c r="AP42" s="54"/>
-      <c r="AQ42" s="54"/>
-      <c r="AR42" s="54"/>
-      <c r="AS42" s="54"/>
-      <c r="AT42" s="54"/>
-      <c r="AU42" s="54"/>
-      <c r="AV42" s="54"/>
-      <c r="AW42" s="54"/>
-      <c r="AX42" s="54"/>
-      <c r="AY42" s="54"/>
-      <c r="AZ42" s="54"/>
-      <c r="BA42" s="54"/>
-      <c r="BB42" s="54"/>
-      <c r="BC42" s="54"/>
-      <c r="BD42" s="54"/>
-      <c r="BE42" s="54"/>
-      <c r="BF42" s="54"/>
-      <c r="BG42" s="54"/>
-      <c r="BH42" s="54"/>
-      <c r="BI42" s="54"/>
-      <c r="BJ42" s="54"/>
-      <c r="BK42" s="54"/>
-      <c r="BL42" s="54"/>
-      <c r="BM42" s="54"/>
-      <c r="BN42" s="54"/>
-      <c r="BO42" s="54"/>
-      <c r="BP42" s="54"/>
-      <c r="BQ42" s="54"/>
-      <c r="BR42" s="54"/>
-      <c r="BS42" s="54"/>
-      <c r="BT42" s="54"/>
-      <c r="BU42" s="54"/>
-      <c r="BV42" s="54"/>
-      <c r="BW42" s="54"/>
-      <c r="BX42" s="54"/>
-      <c r="BY42" s="54"/>
-      <c r="BZ42" s="54"/>
-      <c r="CA42" s="54"/>
-      <c r="CB42" s="54"/>
-      <c r="CC42" s="54"/>
-      <c r="CD42" s="54"/>
-      <c r="CE42" s="54"/>
-      <c r="CF42" s="54"/>
-      <c r="CG42" s="54"/>
-      <c r="CH42" s="54"/>
-      <c r="CI42" s="54"/>
-      <c r="CJ42" s="54"/>
-      <c r="CK42" s="54"/>
-      <c r="CL42" s="54"/>
-      <c r="CM42" s="54"/>
-      <c r="CN42" s="54"/>
-      <c r="CO42" s="54"/>
-      <c r="CP42" s="54"/>
-      <c r="CQ42" s="54"/>
-      <c r="CR42" s="54"/>
-      <c r="CS42" s="54"/>
-      <c r="CT42" s="54"/>
-      <c r="CU42" s="54"/>
-      <c r="CV42" s="54"/>
-      <c r="CW42" s="54"/>
-      <c r="CX42" s="54"/>
-      <c r="CY42" s="54"/>
-      <c r="CZ42" s="54"/>
-      <c r="DA42" s="54"/>
-      <c r="DB42" s="54"/>
-      <c r="DC42" s="54"/>
-      <c r="DD42" s="54"/>
-      <c r="DE42" s="54"/>
-      <c r="DF42" s="54"/>
-      <c r="DG42" s="54"/>
-      <c r="DH42" s="54"/>
-      <c r="DI42" s="54"/>
-      <c r="DJ42" s="54"/>
-      <c r="DK42" s="54"/>
-      <c r="DL42" s="54"/>
-      <c r="DM42" s="54"/>
-      <c r="DN42" s="54"/>
-      <c r="DO42" s="54"/>
-      <c r="DP42" s="54"/>
-      <c r="DQ42" s="54"/>
-      <c r="DR42" s="54"/>
-      <c r="DS42" s="54"/>
-      <c r="DT42" s="54"/>
-      <c r="DU42" s="54"/>
-      <c r="DV42" s="54"/>
-      <c r="DW42" s="54"/>
-      <c r="DX42" s="54"/>
-      <c r="DY42" s="54"/>
-      <c r="DZ42" s="54"/>
-      <c r="EA42" s="54"/>
-      <c r="EB42" s="54"/>
-      <c r="EC42" s="54"/>
-      <c r="ED42" s="54"/>
-      <c r="EE42" s="54"/>
-      <c r="EF42" s="54"/>
-      <c r="EG42" s="54"/>
-      <c r="EH42" s="54"/>
+      <c r="B42" s="64"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="64"/>
+      <c r="H42" s="64"/>
+      <c r="I42" s="64"/>
+      <c r="J42" s="64"/>
+      <c r="K42" s="64"/>
+      <c r="L42" s="64"/>
+      <c r="M42" s="64"/>
+      <c r="N42" s="64"/>
+      <c r="O42" s="64"/>
+      <c r="P42" s="64"/>
+      <c r="Q42" s="64"/>
+      <c r="R42" s="64"/>
+      <c r="S42" s="64"/>
+      <c r="T42" s="64"/>
+      <c r="U42" s="64"/>
+      <c r="V42" s="64"/>
+      <c r="W42" s="64"/>
+      <c r="X42" s="64"/>
+      <c r="Y42" s="64"/>
+      <c r="Z42" s="64"/>
+      <c r="AA42" s="64"/>
+      <c r="AB42" s="64"/>
+      <c r="AC42" s="64"/>
+      <c r="AD42" s="64"/>
+      <c r="AE42" s="64"/>
+      <c r="AF42" s="64"/>
+      <c r="AG42" s="64"/>
+      <c r="AH42" s="64"/>
+      <c r="AI42" s="64"/>
+      <c r="AJ42" s="64"/>
+      <c r="AK42" s="64"/>
+      <c r="AL42" s="64"/>
+      <c r="AM42" s="64"/>
+      <c r="AN42" s="64"/>
+      <c r="AO42" s="64"/>
+      <c r="AP42" s="64"/>
+      <c r="AQ42" s="64"/>
+      <c r="AR42" s="64"/>
+      <c r="AS42" s="64"/>
+      <c r="AT42" s="64"/>
+      <c r="AU42" s="64"/>
+      <c r="AV42" s="64"/>
+      <c r="AW42" s="64"/>
+      <c r="AX42" s="64"/>
+      <c r="AY42" s="64"/>
+      <c r="AZ42" s="64"/>
+      <c r="BA42" s="64"/>
+      <c r="BB42" s="64"/>
+      <c r="BC42" s="64"/>
+      <c r="BD42" s="64"/>
+      <c r="BE42" s="64"/>
+      <c r="BF42" s="64"/>
+      <c r="BG42" s="64"/>
+      <c r="BH42" s="64"/>
+      <c r="BI42" s="64"/>
+      <c r="BJ42" s="64"/>
+      <c r="BK42" s="64"/>
+      <c r="BL42" s="64"/>
+      <c r="BM42" s="64"/>
+      <c r="BN42" s="64"/>
+      <c r="BO42" s="64"/>
+      <c r="BP42" s="64"/>
+      <c r="BQ42" s="64"/>
+      <c r="BR42" s="64"/>
+      <c r="BS42" s="64"/>
+      <c r="BT42" s="64"/>
+      <c r="BU42" s="64"/>
+      <c r="BV42" s="64"/>
+      <c r="BW42" s="64"/>
+      <c r="BX42" s="64"/>
+      <c r="BY42" s="64"/>
+      <c r="BZ42" s="64"/>
+      <c r="CA42" s="64"/>
+      <c r="CB42" s="64"/>
+      <c r="CC42" s="64"/>
+      <c r="CD42" s="64"/>
+      <c r="CE42" s="64"/>
+      <c r="CF42" s="64"/>
+      <c r="CG42" s="64"/>
+      <c r="CH42" s="64"/>
+      <c r="CI42" s="64"/>
+      <c r="CJ42" s="64"/>
+      <c r="CK42" s="64"/>
+      <c r="CL42" s="64"/>
+      <c r="CM42" s="64"/>
+      <c r="CN42" s="64"/>
+      <c r="CO42" s="64"/>
+      <c r="CP42" s="64"/>
+      <c r="CQ42" s="64"/>
+      <c r="CR42" s="64"/>
+      <c r="CS42" s="64"/>
+      <c r="CT42" s="64"/>
+      <c r="CU42" s="64"/>
+      <c r="CV42" s="64"/>
+      <c r="CW42" s="64"/>
+      <c r="CX42" s="64"/>
+      <c r="CY42" s="64"/>
+      <c r="CZ42" s="64"/>
+      <c r="DA42" s="64"/>
+      <c r="DB42" s="64"/>
+      <c r="DC42" s="64"/>
+      <c r="DD42" s="64"/>
+      <c r="DE42" s="64"/>
+      <c r="DF42" s="64"/>
+      <c r="DG42" s="64"/>
+      <c r="DH42" s="64"/>
+      <c r="DI42" s="64"/>
+      <c r="DJ42" s="64"/>
+      <c r="DK42" s="64"/>
+      <c r="DL42" s="64"/>
+      <c r="DM42" s="64"/>
+      <c r="DN42" s="64"/>
+      <c r="DO42" s="64"/>
+      <c r="DP42" s="64"/>
+      <c r="DQ42" s="64"/>
+      <c r="DR42" s="64"/>
+      <c r="DS42" s="64"/>
+      <c r="DT42" s="64"/>
+      <c r="DU42" s="64"/>
+      <c r="DV42" s="64"/>
+      <c r="DW42" s="64"/>
+      <c r="DX42" s="64"/>
+      <c r="DY42" s="64"/>
+      <c r="DZ42" s="64"/>
+      <c r="EA42" s="64"/>
+      <c r="EB42" s="64"/>
+      <c r="EC42" s="64"/>
+      <c r="ED42" s="64"/>
+      <c r="EE42" s="64"/>
+      <c r="EF42" s="64"/>
+      <c r="EG42" s="64"/>
+      <c r="EH42" s="64"/>
     </row>
     <row r="43" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A43" s="55" t="s">
+      <c r="A43" s="65" t="s">
         <v>122</v>
       </c>
-      <c r="B43" s="56" t="s">
+      <c r="B43" s="58" t="s">
         <v>123</v>
       </c>
-      <c r="C43" s="57" t="s">
+      <c r="C43" s="66" t="s">
         <v>95</v>
       </c>
       <c r="D43" s="9" t="s">
@@ -25075,9 +25075,9 @@
       </c>
     </row>
     <row r="44" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A44" s="55"/>
-      <c r="B44" s="55"/>
-      <c r="C44" s="55"/>
+      <c r="A44" s="65"/>
+      <c r="B44" s="65"/>
+      <c r="C44" s="65"/>
       <c r="D44" s="12" t="s">
         <v>80</v>
       </c>
@@ -25617,13 +25617,13 @@
       </c>
     </row>
     <row r="45" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A45" s="55" t="s">
+      <c r="A45" s="65" t="s">
         <v>124</v>
       </c>
-      <c r="B45" s="56" t="s">
+      <c r="B45" s="58" t="s">
         <v>125</v>
       </c>
-      <c r="C45" s="57" t="s">
+      <c r="C45" s="66" t="s">
         <v>95</v>
       </c>
       <c r="D45" s="9" t="s">
@@ -26165,9 +26165,9 @@
       </c>
     </row>
     <row r="46" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A46" s="55"/>
-      <c r="B46" s="55"/>
-      <c r="C46" s="55"/>
+      <c r="A46" s="65"/>
+      <c r="B46" s="65"/>
+      <c r="C46" s="65"/>
       <c r="D46" s="12" t="s">
         <v>80</v>
       </c>
@@ -26707,13 +26707,13 @@
       </c>
     </row>
     <row r="47" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A47" s="55" t="s">
+      <c r="A47" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="B47" s="56" t="s">
+      <c r="B47" s="58" t="s">
         <v>127</v>
       </c>
-      <c r="C47" s="57" t="s">
+      <c r="C47" s="66" t="s">
         <v>95</v>
       </c>
       <c r="D47" s="9" t="s">
@@ -27255,9 +27255,9 @@
       </c>
     </row>
     <row r="48" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A48" s="55"/>
-      <c r="B48" s="55"/>
-      <c r="C48" s="55"/>
+      <c r="A48" s="65"/>
+      <c r="B48" s="65"/>
+      <c r="C48" s="65"/>
       <c r="D48" s="12" t="s">
         <v>80</v>
       </c>
@@ -27797,13 +27797,13 @@
       </c>
     </row>
     <row r="49" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A49" s="55" t="s">
+      <c r="A49" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="B49" s="56" t="s">
+      <c r="B49" s="58" t="s">
         <v>129</v>
       </c>
-      <c r="C49" s="57" t="s">
+      <c r="C49" s="66" t="s">
         <v>86</v>
       </c>
       <c r="D49" s="9" t="s">
@@ -28345,9 +28345,9 @@
       </c>
     </row>
     <row r="50" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A50" s="55"/>
-      <c r="B50" s="55"/>
-      <c r="C50" s="55"/>
+      <c r="A50" s="65"/>
+      <c r="B50" s="65"/>
+      <c r="C50" s="65"/>
       <c r="D50" s="12" t="s">
         <v>80</v>
       </c>
@@ -28883,13 +28883,13 @@
       </c>
     </row>
     <row r="51" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A51" s="55" t="s">
+      <c r="A51" s="65" t="s">
         <v>130</v>
       </c>
-      <c r="B51" s="56" t="s">
+      <c r="B51" s="58" t="s">
         <v>131</v>
       </c>
-      <c r="C51" s="57" t="s">
+      <c r="C51" s="66" t="s">
         <v>95</v>
       </c>
       <c r="D51" s="9" t="s">
@@ -29431,9 +29431,9 @@
       </c>
     </row>
     <row r="52" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A52" s="55"/>
-      <c r="B52" s="55"/>
-      <c r="C52" s="55"/>
+      <c r="A52" s="65"/>
+      <c r="B52" s="65"/>
+      <c r="C52" s="65"/>
       <c r="D52" s="12" t="s">
         <v>80</v>
       </c>
@@ -29973,13 +29973,13 @@
       </c>
     </row>
     <row r="53" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A53" s="55" t="s">
+      <c r="A53" s="65" t="s">
         <v>132</v>
       </c>
-      <c r="B53" s="56" t="s">
+      <c r="B53" s="58" t="s">
         <v>133</v>
       </c>
-      <c r="C53" s="57" t="s">
+      <c r="C53" s="66" t="s">
         <v>95</v>
       </c>
       <c r="D53" s="9" t="s">
@@ -30521,9 +30521,9 @@
       </c>
     </row>
     <row r="54" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A54" s="55"/>
-      <c r="B54" s="55"/>
-      <c r="C54" s="55"/>
+      <c r="A54" s="65"/>
+      <c r="B54" s="65"/>
+      <c r="C54" s="65"/>
       <c r="D54" s="12" t="s">
         <v>80</v>
       </c>
@@ -31063,155 +31063,155 @@
       </c>
     </row>
     <row r="55" spans="1:138" ht="15.75" customHeight="1">
-      <c r="A55" s="54" t="s">
+      <c r="A55" s="64" t="s">
         <v>134</v>
       </c>
-      <c r="B55" s="54"/>
-      <c r="C55" s="54"/>
-      <c r="D55" s="54"/>
-      <c r="E55" s="54"/>
-      <c r="F55" s="54"/>
-      <c r="G55" s="54"/>
-      <c r="H55" s="54"/>
-      <c r="I55" s="54"/>
-      <c r="J55" s="54"/>
-      <c r="K55" s="54"/>
-      <c r="L55" s="54"/>
-      <c r="M55" s="54"/>
-      <c r="N55" s="54"/>
-      <c r="O55" s="54"/>
-      <c r="P55" s="54"/>
-      <c r="Q55" s="54"/>
-      <c r="R55" s="54"/>
-      <c r="S55" s="54"/>
-      <c r="T55" s="54"/>
-      <c r="U55" s="54"/>
-      <c r="V55" s="54"/>
-      <c r="W55" s="54"/>
-      <c r="X55" s="54"/>
-      <c r="Y55" s="54"/>
-      <c r="Z55" s="54"/>
-      <c r="AA55" s="54"/>
-      <c r="AB55" s="54"/>
-      <c r="AC55" s="54"/>
-      <c r="AD55" s="54"/>
-      <c r="AE55" s="54"/>
-      <c r="AF55" s="54"/>
-      <c r="AG55" s="54"/>
-      <c r="AH55" s="54"/>
-      <c r="AI55" s="54"/>
-      <c r="AJ55" s="54"/>
-      <c r="AK55" s="54"/>
-      <c r="AL55" s="54"/>
-      <c r="AM55" s="54"/>
-      <c r="AN55" s="54"/>
-      <c r="AO55" s="54"/>
-      <c r="AP55" s="54"/>
-      <c r="AQ55" s="54"/>
-      <c r="AR55" s="54"/>
-      <c r="AS55" s="54"/>
-      <c r="AT55" s="54"/>
-      <c r="AU55" s="54"/>
-      <c r="AV55" s="54"/>
-      <c r="AW55" s="54"/>
-      <c r="AX55" s="54"/>
-      <c r="AY55" s="54"/>
-      <c r="AZ55" s="54"/>
-      <c r="BA55" s="54"/>
-      <c r="BB55" s="54"/>
-      <c r="BC55" s="54"/>
-      <c r="BD55" s="54"/>
-      <c r="BE55" s="54"/>
-      <c r="BF55" s="54"/>
-      <c r="BG55" s="54"/>
-      <c r="BH55" s="54"/>
-      <c r="BI55" s="54"/>
-      <c r="BJ55" s="54"/>
-      <c r="BK55" s="54"/>
-      <c r="BL55" s="54"/>
-      <c r="BM55" s="54"/>
-      <c r="BN55" s="54"/>
-      <c r="BO55" s="54"/>
-      <c r="BP55" s="54"/>
-      <c r="BQ55" s="54"/>
-      <c r="BR55" s="54"/>
-      <c r="BS55" s="54"/>
-      <c r="BT55" s="54"/>
-      <c r="BU55" s="54"/>
-      <c r="BV55" s="54"/>
-      <c r="BW55" s="54"/>
-      <c r="BX55" s="54"/>
-      <c r="BY55" s="54"/>
-      <c r="BZ55" s="54"/>
-      <c r="CA55" s="54"/>
-      <c r="CB55" s="54"/>
-      <c r="CC55" s="54"/>
-      <c r="CD55" s="54"/>
-      <c r="CE55" s="54"/>
-      <c r="CF55" s="54"/>
-      <c r="CG55" s="54"/>
-      <c r="CH55" s="54"/>
-      <c r="CI55" s="54"/>
-      <c r="CJ55" s="54"/>
-      <c r="CK55" s="54"/>
-      <c r="CL55" s="54"/>
-      <c r="CM55" s="54"/>
-      <c r="CN55" s="54"/>
-      <c r="CO55" s="54"/>
-      <c r="CP55" s="54"/>
-      <c r="CQ55" s="54"/>
-      <c r="CR55" s="54"/>
-      <c r="CS55" s="54"/>
-      <c r="CT55" s="54"/>
-      <c r="CU55" s="54"/>
-      <c r="CV55" s="54"/>
-      <c r="CW55" s="54"/>
-      <c r="CX55" s="54"/>
-      <c r="CY55" s="54"/>
-      <c r="CZ55" s="54"/>
-      <c r="DA55" s="54"/>
-      <c r="DB55" s="54"/>
-      <c r="DC55" s="54"/>
-      <c r="DD55" s="54"/>
-      <c r="DE55" s="54"/>
-      <c r="DF55" s="54"/>
-      <c r="DG55" s="54"/>
-      <c r="DH55" s="54"/>
-      <c r="DI55" s="54"/>
-      <c r="DJ55" s="54"/>
-      <c r="DK55" s="54"/>
-      <c r="DL55" s="54"/>
-      <c r="DM55" s="54"/>
-      <c r="DN55" s="54"/>
-      <c r="DO55" s="54"/>
-      <c r="DP55" s="54"/>
-      <c r="DQ55" s="54"/>
-      <c r="DR55" s="54"/>
-      <c r="DS55" s="54"/>
-      <c r="DT55" s="54"/>
-      <c r="DU55" s="54"/>
-      <c r="DV55" s="54"/>
-      <c r="DW55" s="54"/>
-      <c r="DX55" s="54"/>
-      <c r="DY55" s="54"/>
-      <c r="DZ55" s="54"/>
-      <c r="EA55" s="54"/>
-      <c r="EB55" s="54"/>
-      <c r="EC55" s="54"/>
-      <c r="ED55" s="54"/>
-      <c r="EE55" s="54"/>
-      <c r="EF55" s="54"/>
-      <c r="EG55" s="54"/>
-      <c r="EH55" s="54"/>
+      <c r="B55" s="64"/>
+      <c r="C55" s="64"/>
+      <c r="D55" s="64"/>
+      <c r="E55" s="64"/>
+      <c r="F55" s="64"/>
+      <c r="G55" s="64"/>
+      <c r="H55" s="64"/>
+      <c r="I55" s="64"/>
+      <c r="J55" s="64"/>
+      <c r="K55" s="64"/>
+      <c r="L55" s="64"/>
+      <c r="M55" s="64"/>
+      <c r="N55" s="64"/>
+      <c r="O55" s="64"/>
+      <c r="P55" s="64"/>
+      <c r="Q55" s="64"/>
+      <c r="R55" s="64"/>
+      <c r="S55" s="64"/>
+      <c r="T55" s="64"/>
+      <c r="U55" s="64"/>
+      <c r="V55" s="64"/>
+      <c r="W55" s="64"/>
+      <c r="X55" s="64"/>
+      <c r="Y55" s="64"/>
+      <c r="Z55" s="64"/>
+      <c r="AA55" s="64"/>
+      <c r="AB55" s="64"/>
+      <c r="AC55" s="64"/>
+      <c r="AD55" s="64"/>
+      <c r="AE55" s="64"/>
+      <c r="AF55" s="64"/>
+      <c r="AG55" s="64"/>
+      <c r="AH55" s="64"/>
+      <c r="AI55" s="64"/>
+      <c r="AJ55" s="64"/>
+      <c r="AK55" s="64"/>
+      <c r="AL55" s="64"/>
+      <c r="AM55" s="64"/>
+      <c r="AN55" s="64"/>
+      <c r="AO55" s="64"/>
+      <c r="AP55" s="64"/>
+      <c r="AQ55" s="64"/>
+      <c r="AR55" s="64"/>
+      <c r="AS55" s="64"/>
+      <c r="AT55" s="64"/>
+      <c r="AU55" s="64"/>
+      <c r="AV55" s="64"/>
+      <c r="AW55" s="64"/>
+      <c r="AX55" s="64"/>
+      <c r="AY55" s="64"/>
+      <c r="AZ55" s="64"/>
+      <c r="BA55" s="64"/>
+      <c r="BB55" s="64"/>
+      <c r="BC55" s="64"/>
+      <c r="BD55" s="64"/>
+      <c r="BE55" s="64"/>
+      <c r="BF55" s="64"/>
+      <c r="BG55" s="64"/>
+      <c r="BH55" s="64"/>
+      <c r="BI55" s="64"/>
+      <c r="BJ55" s="64"/>
+      <c r="BK55" s="64"/>
+      <c r="BL55" s="64"/>
+      <c r="BM55" s="64"/>
+      <c r="BN55" s="64"/>
+      <c r="BO55" s="64"/>
+      <c r="BP55" s="64"/>
+      <c r="BQ55" s="64"/>
+      <c r="BR55" s="64"/>
+      <c r="BS55" s="64"/>
+      <c r="BT55" s="64"/>
+      <c r="BU55" s="64"/>
+      <c r="BV55" s="64"/>
+      <c r="BW55" s="64"/>
+      <c r="BX55" s="64"/>
+      <c r="BY55" s="64"/>
+      <c r="BZ55" s="64"/>
+      <c r="CA55" s="64"/>
+      <c r="CB55" s="64"/>
+      <c r="CC55" s="64"/>
+      <c r="CD55" s="64"/>
+      <c r="CE55" s="64"/>
+      <c r="CF55" s="64"/>
+      <c r="CG55" s="64"/>
+      <c r="CH55" s="64"/>
+      <c r="CI55" s="64"/>
+      <c r="CJ55" s="64"/>
+      <c r="CK55" s="64"/>
+      <c r="CL55" s="64"/>
+      <c r="CM55" s="64"/>
+      <c r="CN55" s="64"/>
+      <c r="CO55" s="64"/>
+      <c r="CP55" s="64"/>
+      <c r="CQ55" s="64"/>
+      <c r="CR55" s="64"/>
+      <c r="CS55" s="64"/>
+      <c r="CT55" s="64"/>
+      <c r="CU55" s="64"/>
+      <c r="CV55" s="64"/>
+      <c r="CW55" s="64"/>
+      <c r="CX55" s="64"/>
+      <c r="CY55" s="64"/>
+      <c r="CZ55" s="64"/>
+      <c r="DA55" s="64"/>
+      <c r="DB55" s="64"/>
+      <c r="DC55" s="64"/>
+      <c r="DD55" s="64"/>
+      <c r="DE55" s="64"/>
+      <c r="DF55" s="64"/>
+      <c r="DG55" s="64"/>
+      <c r="DH55" s="64"/>
+      <c r="DI55" s="64"/>
+      <c r="DJ55" s="64"/>
+      <c r="DK55" s="64"/>
+      <c r="DL55" s="64"/>
+      <c r="DM55" s="64"/>
+      <c r="DN55" s="64"/>
+      <c r="DO55" s="64"/>
+      <c r="DP55" s="64"/>
+      <c r="DQ55" s="64"/>
+      <c r="DR55" s="64"/>
+      <c r="DS55" s="64"/>
+      <c r="DT55" s="64"/>
+      <c r="DU55" s="64"/>
+      <c r="DV55" s="64"/>
+      <c r="DW55" s="64"/>
+      <c r="DX55" s="64"/>
+      <c r="DY55" s="64"/>
+      <c r="DZ55" s="64"/>
+      <c r="EA55" s="64"/>
+      <c r="EB55" s="64"/>
+      <c r="EC55" s="64"/>
+      <c r="ED55" s="64"/>
+      <c r="EE55" s="64"/>
+      <c r="EF55" s="64"/>
+      <c r="EG55" s="64"/>
+      <c r="EH55" s="64"/>
     </row>
     <row r="56" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A56" s="55" t="s">
+      <c r="A56" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="B56" s="56" t="s">
+      <c r="B56" s="58" t="s">
         <v>136</v>
       </c>
-      <c r="C56" s="57" t="s">
+      <c r="C56" s="66" t="s">
         <v>137</v>
       </c>
       <c r="D56" s="9" t="s">
@@ -31753,9 +31753,9 @@
       </c>
     </row>
     <row r="57" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A57" s="55"/>
-      <c r="B57" s="55"/>
-      <c r="C57" s="55"/>
+      <c r="A57" s="65"/>
+      <c r="B57" s="65"/>
+      <c r="C57" s="65"/>
       <c r="D57" s="12" t="s">
         <v>80</v>
       </c>
@@ -32295,13 +32295,13 @@
       </c>
     </row>
     <row r="58" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A58" s="55" t="s">
+      <c r="A58" s="65" t="s">
         <v>138</v>
       </c>
-      <c r="B58" s="56" t="s">
+      <c r="B58" s="58" t="s">
         <v>139</v>
       </c>
-      <c r="C58" s="57" t="s">
+      <c r="C58" s="66" t="s">
         <v>90</v>
       </c>
       <c r="D58" s="9" t="s">
@@ -32843,9 +32843,9 @@
       </c>
     </row>
     <row r="59" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A59" s="55"/>
-      <c r="B59" s="55"/>
-      <c r="C59" s="55"/>
+      <c r="A59" s="65"/>
+      <c r="B59" s="65"/>
+      <c r="C59" s="65"/>
       <c r="D59" s="12" t="s">
         <v>80</v>
       </c>
@@ -33385,13 +33385,13 @@
       </c>
     </row>
     <row r="60" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A60" s="55" t="s">
+      <c r="A60" s="65" t="s">
         <v>140</v>
       </c>
-      <c r="B60" s="56" t="s">
+      <c r="B60" s="58" t="s">
         <v>141</v>
       </c>
-      <c r="C60" s="57" t="s">
+      <c r="C60" s="66" t="s">
         <v>137</v>
       </c>
       <c r="D60" s="9" t="s">
@@ -33933,9 +33933,9 @@
       </c>
     </row>
     <row r="61" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A61" s="55"/>
-      <c r="B61" s="55"/>
-      <c r="C61" s="55"/>
+      <c r="A61" s="65"/>
+      <c r="B61" s="65"/>
+      <c r="C61" s="65"/>
       <c r="D61" s="12" t="s">
         <v>80</v>
       </c>
@@ -34475,13 +34475,13 @@
       </c>
     </row>
     <row r="62" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A62" s="55" t="s">
+      <c r="A62" s="65" t="s">
         <v>142</v>
       </c>
-      <c r="B62" s="56" t="s">
+      <c r="B62" s="58" t="s">
         <v>143</v>
       </c>
-      <c r="C62" s="57" t="s">
+      <c r="C62" s="66" t="s">
         <v>137</v>
       </c>
       <c r="D62" s="9" t="s">
@@ -35023,9 +35023,9 @@
       </c>
     </row>
     <row r="63" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A63" s="55"/>
-      <c r="B63" s="55"/>
-      <c r="C63" s="55"/>
+      <c r="A63" s="65"/>
+      <c r="B63" s="65"/>
+      <c r="C63" s="65"/>
       <c r="D63" s="12" t="s">
         <v>80</v>
       </c>
@@ -35565,13 +35565,13 @@
       </c>
     </row>
     <row r="64" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A64" s="55" t="s">
+      <c r="A64" s="65" t="s">
         <v>144</v>
       </c>
-      <c r="B64" s="56" t="s">
+      <c r="B64" s="58" t="s">
         <v>145</v>
       </c>
-      <c r="C64" s="57" t="s">
+      <c r="C64" s="66" t="s">
         <v>86</v>
       </c>
       <c r="D64" s="9" t="s">
@@ -36113,9 +36113,9 @@
       </c>
     </row>
     <row r="65" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A65" s="55"/>
-      <c r="B65" s="55"/>
-      <c r="C65" s="55"/>
+      <c r="A65" s="65"/>
+      <c r="B65" s="65"/>
+      <c r="C65" s="65"/>
       <c r="D65" s="12" t="s">
         <v>80</v>
       </c>
@@ -36651,13 +36651,13 @@
       </c>
     </row>
     <row r="66" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A66" s="55" t="s">
+      <c r="A66" s="65" t="s">
         <v>146</v>
       </c>
-      <c r="B66" s="56" t="s">
+      <c r="B66" s="58" t="s">
         <v>147</v>
       </c>
-      <c r="C66" s="57" t="s">
+      <c r="C66" s="66" t="s">
         <v>90</v>
       </c>
       <c r="D66" s="9" t="s">
@@ -37199,9 +37199,9 @@
       </c>
     </row>
     <row r="67" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A67" s="55"/>
-      <c r="B67" s="55"/>
-      <c r="C67" s="55"/>
+      <c r="A67" s="65"/>
+      <c r="B67" s="65"/>
+      <c r="C67" s="65"/>
       <c r="D67" s="12" t="s">
         <v>80</v>
       </c>
@@ -37741,155 +37741,155 @@
       </c>
     </row>
     <row r="68" spans="1:138" ht="15.75" customHeight="1">
-      <c r="A68" s="54" t="s">
+      <c r="A68" s="64" t="s">
         <v>148</v>
       </c>
-      <c r="B68" s="54"/>
-      <c r="C68" s="54"/>
-      <c r="D68" s="54"/>
-      <c r="E68" s="54"/>
-      <c r="F68" s="54"/>
-      <c r="G68" s="54"/>
-      <c r="H68" s="54"/>
-      <c r="I68" s="54"/>
-      <c r="J68" s="54"/>
-      <c r="K68" s="54"/>
-      <c r="L68" s="54"/>
-      <c r="M68" s="54"/>
-      <c r="N68" s="54"/>
-      <c r="O68" s="54"/>
-      <c r="P68" s="54"/>
-      <c r="Q68" s="54"/>
-      <c r="R68" s="54"/>
-      <c r="S68" s="54"/>
-      <c r="T68" s="54"/>
-      <c r="U68" s="54"/>
-      <c r="V68" s="54"/>
-      <c r="W68" s="54"/>
-      <c r="X68" s="54"/>
-      <c r="Y68" s="54"/>
-      <c r="Z68" s="54"/>
-      <c r="AA68" s="54"/>
-      <c r="AB68" s="54"/>
-      <c r="AC68" s="54"/>
-      <c r="AD68" s="54"/>
-      <c r="AE68" s="54"/>
-      <c r="AF68" s="54"/>
-      <c r="AG68" s="54"/>
-      <c r="AH68" s="54"/>
-      <c r="AI68" s="54"/>
-      <c r="AJ68" s="54"/>
-      <c r="AK68" s="54"/>
-      <c r="AL68" s="54"/>
-      <c r="AM68" s="54"/>
-      <c r="AN68" s="54"/>
-      <c r="AO68" s="54"/>
-      <c r="AP68" s="54"/>
-      <c r="AQ68" s="54"/>
-      <c r="AR68" s="54"/>
-      <c r="AS68" s="54"/>
-      <c r="AT68" s="54"/>
-      <c r="AU68" s="54"/>
-      <c r="AV68" s="54"/>
-      <c r="AW68" s="54"/>
-      <c r="AX68" s="54"/>
-      <c r="AY68" s="54"/>
-      <c r="AZ68" s="54"/>
-      <c r="BA68" s="54"/>
-      <c r="BB68" s="54"/>
-      <c r="BC68" s="54"/>
-      <c r="BD68" s="54"/>
-      <c r="BE68" s="54"/>
-      <c r="BF68" s="54"/>
-      <c r="BG68" s="54"/>
-      <c r="BH68" s="54"/>
-      <c r="BI68" s="54"/>
-      <c r="BJ68" s="54"/>
-      <c r="BK68" s="54"/>
-      <c r="BL68" s="54"/>
-      <c r="BM68" s="54"/>
-      <c r="BN68" s="54"/>
-      <c r="BO68" s="54"/>
-      <c r="BP68" s="54"/>
-      <c r="BQ68" s="54"/>
-      <c r="BR68" s="54"/>
-      <c r="BS68" s="54"/>
-      <c r="BT68" s="54"/>
-      <c r="BU68" s="54"/>
-      <c r="BV68" s="54"/>
-      <c r="BW68" s="54"/>
-      <c r="BX68" s="54"/>
-      <c r="BY68" s="54"/>
-      <c r="BZ68" s="54"/>
-      <c r="CA68" s="54"/>
-      <c r="CB68" s="54"/>
-      <c r="CC68" s="54"/>
-      <c r="CD68" s="54"/>
-      <c r="CE68" s="54"/>
-      <c r="CF68" s="54"/>
-      <c r="CG68" s="54"/>
-      <c r="CH68" s="54"/>
-      <c r="CI68" s="54"/>
-      <c r="CJ68" s="54"/>
-      <c r="CK68" s="54"/>
-      <c r="CL68" s="54"/>
-      <c r="CM68" s="54"/>
-      <c r="CN68" s="54"/>
-      <c r="CO68" s="54"/>
-      <c r="CP68" s="54"/>
-      <c r="CQ68" s="54"/>
-      <c r="CR68" s="54"/>
-      <c r="CS68" s="54"/>
-      <c r="CT68" s="54"/>
-      <c r="CU68" s="54"/>
-      <c r="CV68" s="54"/>
-      <c r="CW68" s="54"/>
-      <c r="CX68" s="54"/>
-      <c r="CY68" s="54"/>
-      <c r="CZ68" s="54"/>
-      <c r="DA68" s="54"/>
-      <c r="DB68" s="54"/>
-      <c r="DC68" s="54"/>
-      <c r="DD68" s="54"/>
-      <c r="DE68" s="54"/>
-      <c r="DF68" s="54"/>
-      <c r="DG68" s="54"/>
-      <c r="DH68" s="54"/>
-      <c r="DI68" s="54"/>
-      <c r="DJ68" s="54"/>
-      <c r="DK68" s="54"/>
-      <c r="DL68" s="54"/>
-      <c r="DM68" s="54"/>
-      <c r="DN68" s="54"/>
-      <c r="DO68" s="54"/>
-      <c r="DP68" s="54"/>
-      <c r="DQ68" s="54"/>
-      <c r="DR68" s="54"/>
-      <c r="DS68" s="54"/>
-      <c r="DT68" s="54"/>
-      <c r="DU68" s="54"/>
-      <c r="DV68" s="54"/>
-      <c r="DW68" s="54"/>
-      <c r="DX68" s="54"/>
-      <c r="DY68" s="54"/>
-      <c r="DZ68" s="54"/>
-      <c r="EA68" s="54"/>
-      <c r="EB68" s="54"/>
-      <c r="EC68" s="54"/>
-      <c r="ED68" s="54"/>
-      <c r="EE68" s="54"/>
-      <c r="EF68" s="54"/>
-      <c r="EG68" s="54"/>
-      <c r="EH68" s="54"/>
+      <c r="B68" s="64"/>
+      <c r="C68" s="64"/>
+      <c r="D68" s="64"/>
+      <c r="E68" s="64"/>
+      <c r="F68" s="64"/>
+      <c r="G68" s="64"/>
+      <c r="H68" s="64"/>
+      <c r="I68" s="64"/>
+      <c r="J68" s="64"/>
+      <c r="K68" s="64"/>
+      <c r="L68" s="64"/>
+      <c r="M68" s="64"/>
+      <c r="N68" s="64"/>
+      <c r="O68" s="64"/>
+      <c r="P68" s="64"/>
+      <c r="Q68" s="64"/>
+      <c r="R68" s="64"/>
+      <c r="S68" s="64"/>
+      <c r="T68" s="64"/>
+      <c r="U68" s="64"/>
+      <c r="V68" s="64"/>
+      <c r="W68" s="64"/>
+      <c r="X68" s="64"/>
+      <c r="Y68" s="64"/>
+      <c r="Z68" s="64"/>
+      <c r="AA68" s="64"/>
+      <c r="AB68" s="64"/>
+      <c r="AC68" s="64"/>
+      <c r="AD68" s="64"/>
+      <c r="AE68" s="64"/>
+      <c r="AF68" s="64"/>
+      <c r="AG68" s="64"/>
+      <c r="AH68" s="64"/>
+      <c r="AI68" s="64"/>
+      <c r="AJ68" s="64"/>
+      <c r="AK68" s="64"/>
+      <c r="AL68" s="64"/>
+      <c r="AM68" s="64"/>
+      <c r="AN68" s="64"/>
+      <c r="AO68" s="64"/>
+      <c r="AP68" s="64"/>
+      <c r="AQ68" s="64"/>
+      <c r="AR68" s="64"/>
+      <c r="AS68" s="64"/>
+      <c r="AT68" s="64"/>
+      <c r="AU68" s="64"/>
+      <c r="AV68" s="64"/>
+      <c r="AW68" s="64"/>
+      <c r="AX68" s="64"/>
+      <c r="AY68" s="64"/>
+      <c r="AZ68" s="64"/>
+      <c r="BA68" s="64"/>
+      <c r="BB68" s="64"/>
+      <c r="BC68" s="64"/>
+      <c r="BD68" s="64"/>
+      <c r="BE68" s="64"/>
+      <c r="BF68" s="64"/>
+      <c r="BG68" s="64"/>
+      <c r="BH68" s="64"/>
+      <c r="BI68" s="64"/>
+      <c r="BJ68" s="64"/>
+      <c r="BK68" s="64"/>
+      <c r="BL68" s="64"/>
+      <c r="BM68" s="64"/>
+      <c r="BN68" s="64"/>
+      <c r="BO68" s="64"/>
+      <c r="BP68" s="64"/>
+      <c r="BQ68" s="64"/>
+      <c r="BR68" s="64"/>
+      <c r="BS68" s="64"/>
+      <c r="BT68" s="64"/>
+      <c r="BU68" s="64"/>
+      <c r="BV68" s="64"/>
+      <c r="BW68" s="64"/>
+      <c r="BX68" s="64"/>
+      <c r="BY68" s="64"/>
+      <c r="BZ68" s="64"/>
+      <c r="CA68" s="64"/>
+      <c r="CB68" s="64"/>
+      <c r="CC68" s="64"/>
+      <c r="CD68" s="64"/>
+      <c r="CE68" s="64"/>
+      <c r="CF68" s="64"/>
+      <c r="CG68" s="64"/>
+      <c r="CH68" s="64"/>
+      <c r="CI68" s="64"/>
+      <c r="CJ68" s="64"/>
+      <c r="CK68" s="64"/>
+      <c r="CL68" s="64"/>
+      <c r="CM68" s="64"/>
+      <c r="CN68" s="64"/>
+      <c r="CO68" s="64"/>
+      <c r="CP68" s="64"/>
+      <c r="CQ68" s="64"/>
+      <c r="CR68" s="64"/>
+      <c r="CS68" s="64"/>
+      <c r="CT68" s="64"/>
+      <c r="CU68" s="64"/>
+      <c r="CV68" s="64"/>
+      <c r="CW68" s="64"/>
+      <c r="CX68" s="64"/>
+      <c r="CY68" s="64"/>
+      <c r="CZ68" s="64"/>
+      <c r="DA68" s="64"/>
+      <c r="DB68" s="64"/>
+      <c r="DC68" s="64"/>
+      <c r="DD68" s="64"/>
+      <c r="DE68" s="64"/>
+      <c r="DF68" s="64"/>
+      <c r="DG68" s="64"/>
+      <c r="DH68" s="64"/>
+      <c r="DI68" s="64"/>
+      <c r="DJ68" s="64"/>
+      <c r="DK68" s="64"/>
+      <c r="DL68" s="64"/>
+      <c r="DM68" s="64"/>
+      <c r="DN68" s="64"/>
+      <c r="DO68" s="64"/>
+      <c r="DP68" s="64"/>
+      <c r="DQ68" s="64"/>
+      <c r="DR68" s="64"/>
+      <c r="DS68" s="64"/>
+      <c r="DT68" s="64"/>
+      <c r="DU68" s="64"/>
+      <c r="DV68" s="64"/>
+      <c r="DW68" s="64"/>
+      <c r="DX68" s="64"/>
+      <c r="DY68" s="64"/>
+      <c r="DZ68" s="64"/>
+      <c r="EA68" s="64"/>
+      <c r="EB68" s="64"/>
+      <c r="EC68" s="64"/>
+      <c r="ED68" s="64"/>
+      <c r="EE68" s="64"/>
+      <c r="EF68" s="64"/>
+      <c r="EG68" s="64"/>
+      <c r="EH68" s="64"/>
     </row>
     <row r="69" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A69" s="55" t="s">
+      <c r="A69" s="65" t="s">
         <v>149</v>
       </c>
-      <c r="B69" s="56" t="s">
+      <c r="B69" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="C69" s="57" t="s">
+      <c r="C69" s="66" t="s">
         <v>137</v>
       </c>
       <c r="D69" s="9" t="s">
@@ -38431,9 +38431,9 @@
       </c>
     </row>
     <row r="70" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A70" s="55"/>
-      <c r="B70" s="55"/>
-      <c r="C70" s="55"/>
+      <c r="A70" s="65"/>
+      <c r="B70" s="65"/>
+      <c r="C70" s="65"/>
       <c r="D70" s="12" t="s">
         <v>80</v>
       </c>
@@ -38973,13 +38973,13 @@
       </c>
     </row>
     <row r="71" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A71" s="55" t="s">
+      <c r="A71" s="65" t="s">
         <v>151</v>
       </c>
-      <c r="B71" s="56" t="s">
+      <c r="B71" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="C71" s="57" t="s">
+      <c r="C71" s="66" t="s">
         <v>137</v>
       </c>
       <c r="D71" s="9" t="s">
@@ -39521,9 +39521,9 @@
       </c>
     </row>
     <row r="72" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A72" s="55"/>
-      <c r="B72" s="55"/>
-      <c r="C72" s="55"/>
+      <c r="A72" s="65"/>
+      <c r="B72" s="65"/>
+      <c r="C72" s="65"/>
       <c r="D72" s="12" t="s">
         <v>80</v>
       </c>
@@ -40063,13 +40063,13 @@
       </c>
     </row>
     <row r="73" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A73" s="55" t="s">
+      <c r="A73" s="65" t="s">
         <v>153</v>
       </c>
-      <c r="B73" s="56" t="s">
+      <c r="B73" s="58" t="s">
         <v>154</v>
       </c>
-      <c r="C73" s="57" t="s">
+      <c r="C73" s="66" t="s">
         <v>137</v>
       </c>
       <c r="D73" s="9" t="s">
@@ -40611,9 +40611,9 @@
       </c>
     </row>
     <row r="74" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A74" s="55"/>
-      <c r="B74" s="55"/>
-      <c r="C74" s="55"/>
+      <c r="A74" s="65"/>
+      <c r="B74" s="65"/>
+      <c r="C74" s="65"/>
       <c r="D74" s="12" t="s">
         <v>80</v>
       </c>
@@ -41153,13 +41153,13 @@
       </c>
     </row>
     <row r="75" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A75" s="55" t="s">
+      <c r="A75" s="65" t="s">
         <v>155</v>
       </c>
-      <c r="B75" s="56" t="s">
+      <c r="B75" s="58" t="s">
         <v>156</v>
       </c>
-      <c r="C75" s="57" t="s">
+      <c r="C75" s="66" t="s">
         <v>137</v>
       </c>
       <c r="D75" s="9" t="s">
@@ -41701,9 +41701,9 @@
       </c>
     </row>
     <row r="76" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A76" s="55"/>
-      <c r="B76" s="55"/>
-      <c r="C76" s="55"/>
+      <c r="A76" s="65"/>
+      <c r="B76" s="65"/>
+      <c r="C76" s="65"/>
       <c r="D76" s="12" t="s">
         <v>80</v>
       </c>
@@ -42243,13 +42243,13 @@
       </c>
     </row>
     <row r="77" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A77" s="55" t="s">
+      <c r="A77" s="65" t="s">
         <v>157</v>
       </c>
-      <c r="B77" s="56" t="s">
+      <c r="B77" s="58" t="s">
         <v>158</v>
       </c>
-      <c r="C77" s="57" t="s">
+      <c r="C77" s="66" t="s">
         <v>90</v>
       </c>
       <c r="D77" s="9" t="s">
@@ -42791,9 +42791,9 @@
       </c>
     </row>
     <row r="78" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A78" s="55"/>
-      <c r="B78" s="55"/>
-      <c r="C78" s="55"/>
+      <c r="A78" s="65"/>
+      <c r="B78" s="65"/>
+      <c r="C78" s="65"/>
       <c r="D78" s="12" t="s">
         <v>80</v>
       </c>
@@ -43333,155 +43333,155 @@
       </c>
     </row>
     <row r="79" spans="1:138" ht="15.75" customHeight="1">
-      <c r="A79" s="54" t="s">
+      <c r="A79" s="64" t="s">
         <v>159</v>
       </c>
-      <c r="B79" s="54"/>
-      <c r="C79" s="54"/>
-      <c r="D79" s="54"/>
-      <c r="E79" s="54"/>
-      <c r="F79" s="54"/>
-      <c r="G79" s="54"/>
-      <c r="H79" s="54"/>
-      <c r="I79" s="54"/>
-      <c r="J79" s="54"/>
-      <c r="K79" s="54"/>
-      <c r="L79" s="54"/>
-      <c r="M79" s="54"/>
-      <c r="N79" s="54"/>
-      <c r="O79" s="54"/>
-      <c r="P79" s="54"/>
-      <c r="Q79" s="54"/>
-      <c r="R79" s="54"/>
-      <c r="S79" s="54"/>
-      <c r="T79" s="54"/>
-      <c r="U79" s="54"/>
-      <c r="V79" s="54"/>
-      <c r="W79" s="54"/>
-      <c r="X79" s="54"/>
-      <c r="Y79" s="54"/>
-      <c r="Z79" s="54"/>
-      <c r="AA79" s="54"/>
-      <c r="AB79" s="54"/>
-      <c r="AC79" s="54"/>
-      <c r="AD79" s="54"/>
-      <c r="AE79" s="54"/>
-      <c r="AF79" s="54"/>
-      <c r="AG79" s="54"/>
-      <c r="AH79" s="54"/>
-      <c r="AI79" s="54"/>
-      <c r="AJ79" s="54"/>
-      <c r="AK79" s="54"/>
-      <c r="AL79" s="54"/>
-      <c r="AM79" s="54"/>
-      <c r="AN79" s="54"/>
-      <c r="AO79" s="54"/>
-      <c r="AP79" s="54"/>
-      <c r="AQ79" s="54"/>
-      <c r="AR79" s="54"/>
-      <c r="AS79" s="54"/>
-      <c r="AT79" s="54"/>
-      <c r="AU79" s="54"/>
-      <c r="AV79" s="54"/>
-      <c r="AW79" s="54"/>
-      <c r="AX79" s="54"/>
-      <c r="AY79" s="54"/>
-      <c r="AZ79" s="54"/>
-      <c r="BA79" s="54"/>
-      <c r="BB79" s="54"/>
-      <c r="BC79" s="54"/>
-      <c r="BD79" s="54"/>
-      <c r="BE79" s="54"/>
-      <c r="BF79" s="54"/>
-      <c r="BG79" s="54"/>
-      <c r="BH79" s="54"/>
-      <c r="BI79" s="54"/>
-      <c r="BJ79" s="54"/>
-      <c r="BK79" s="54"/>
-      <c r="BL79" s="54"/>
-      <c r="BM79" s="54"/>
-      <c r="BN79" s="54"/>
-      <c r="BO79" s="54"/>
-      <c r="BP79" s="54"/>
-      <c r="BQ79" s="54"/>
-      <c r="BR79" s="54"/>
-      <c r="BS79" s="54"/>
-      <c r="BT79" s="54"/>
-      <c r="BU79" s="54"/>
-      <c r="BV79" s="54"/>
-      <c r="BW79" s="54"/>
-      <c r="BX79" s="54"/>
-      <c r="BY79" s="54"/>
-      <c r="BZ79" s="54"/>
-      <c r="CA79" s="54"/>
-      <c r="CB79" s="54"/>
-      <c r="CC79" s="54"/>
-      <c r="CD79" s="54"/>
-      <c r="CE79" s="54"/>
-      <c r="CF79" s="54"/>
-      <c r="CG79" s="54"/>
-      <c r="CH79" s="54"/>
-      <c r="CI79" s="54"/>
-      <c r="CJ79" s="54"/>
-      <c r="CK79" s="54"/>
-      <c r="CL79" s="54"/>
-      <c r="CM79" s="54"/>
-      <c r="CN79" s="54"/>
-      <c r="CO79" s="54"/>
-      <c r="CP79" s="54"/>
-      <c r="CQ79" s="54"/>
-      <c r="CR79" s="54"/>
-      <c r="CS79" s="54"/>
-      <c r="CT79" s="54"/>
-      <c r="CU79" s="54"/>
-      <c r="CV79" s="54"/>
-      <c r="CW79" s="54"/>
-      <c r="CX79" s="54"/>
-      <c r="CY79" s="54"/>
-      <c r="CZ79" s="54"/>
-      <c r="DA79" s="54"/>
-      <c r="DB79" s="54"/>
-      <c r="DC79" s="54"/>
-      <c r="DD79" s="54"/>
-      <c r="DE79" s="54"/>
-      <c r="DF79" s="54"/>
-      <c r="DG79" s="54"/>
-      <c r="DH79" s="54"/>
-      <c r="DI79" s="54"/>
-      <c r="DJ79" s="54"/>
-      <c r="DK79" s="54"/>
-      <c r="DL79" s="54"/>
-      <c r="DM79" s="54"/>
-      <c r="DN79" s="54"/>
-      <c r="DO79" s="54"/>
-      <c r="DP79" s="54"/>
-      <c r="DQ79" s="54"/>
-      <c r="DR79" s="54"/>
-      <c r="DS79" s="54"/>
-      <c r="DT79" s="54"/>
-      <c r="DU79" s="54"/>
-      <c r="DV79" s="54"/>
-      <c r="DW79" s="54"/>
-      <c r="DX79" s="54"/>
-      <c r="DY79" s="54"/>
-      <c r="DZ79" s="54"/>
-      <c r="EA79" s="54"/>
-      <c r="EB79" s="54"/>
-      <c r="EC79" s="54"/>
-      <c r="ED79" s="54"/>
-      <c r="EE79" s="54"/>
-      <c r="EF79" s="54"/>
-      <c r="EG79" s="54"/>
-      <c r="EH79" s="54"/>
+      <c r="B79" s="64"/>
+      <c r="C79" s="64"/>
+      <c r="D79" s="64"/>
+      <c r="E79" s="64"/>
+      <c r="F79" s="64"/>
+      <c r="G79" s="64"/>
+      <c r="H79" s="64"/>
+      <c r="I79" s="64"/>
+      <c r="J79" s="64"/>
+      <c r="K79" s="64"/>
+      <c r="L79" s="64"/>
+      <c r="M79" s="64"/>
+      <c r="N79" s="64"/>
+      <c r="O79" s="64"/>
+      <c r="P79" s="64"/>
+      <c r="Q79" s="64"/>
+      <c r="R79" s="64"/>
+      <c r="S79" s="64"/>
+      <c r="T79" s="64"/>
+      <c r="U79" s="64"/>
+      <c r="V79" s="64"/>
+      <c r="W79" s="64"/>
+      <c r="X79" s="64"/>
+      <c r="Y79" s="64"/>
+      <c r="Z79" s="64"/>
+      <c r="AA79" s="64"/>
+      <c r="AB79" s="64"/>
+      <c r="AC79" s="64"/>
+      <c r="AD79" s="64"/>
+      <c r="AE79" s="64"/>
+      <c r="AF79" s="64"/>
+      <c r="AG79" s="64"/>
+      <c r="AH79" s="64"/>
+      <c r="AI79" s="64"/>
+      <c r="AJ79" s="64"/>
+      <c r="AK79" s="64"/>
+      <c r="AL79" s="64"/>
+      <c r="AM79" s="64"/>
+      <c r="AN79" s="64"/>
+      <c r="AO79" s="64"/>
+      <c r="AP79" s="64"/>
+      <c r="AQ79" s="64"/>
+      <c r="AR79" s="64"/>
+      <c r="AS79" s="64"/>
+      <c r="AT79" s="64"/>
+      <c r="AU79" s="64"/>
+      <c r="AV79" s="64"/>
+      <c r="AW79" s="64"/>
+      <c r="AX79" s="64"/>
+      <c r="AY79" s="64"/>
+      <c r="AZ79" s="64"/>
+      <c r="BA79" s="64"/>
+      <c r="BB79" s="64"/>
+      <c r="BC79" s="64"/>
+      <c r="BD79" s="64"/>
+      <c r="BE79" s="64"/>
+      <c r="BF79" s="64"/>
+      <c r="BG79" s="64"/>
+      <c r="BH79" s="64"/>
+      <c r="BI79" s="64"/>
+      <c r="BJ79" s="64"/>
+      <c r="BK79" s="64"/>
+      <c r="BL79" s="64"/>
+      <c r="BM79" s="64"/>
+      <c r="BN79" s="64"/>
+      <c r="BO79" s="64"/>
+      <c r="BP79" s="64"/>
+      <c r="BQ79" s="64"/>
+      <c r="BR79" s="64"/>
+      <c r="BS79" s="64"/>
+      <c r="BT79" s="64"/>
+      <c r="BU79" s="64"/>
+      <c r="BV79" s="64"/>
+      <c r="BW79" s="64"/>
+      <c r="BX79" s="64"/>
+      <c r="BY79" s="64"/>
+      <c r="BZ79" s="64"/>
+      <c r="CA79" s="64"/>
+      <c r="CB79" s="64"/>
+      <c r="CC79" s="64"/>
+      <c r="CD79" s="64"/>
+      <c r="CE79" s="64"/>
+      <c r="CF79" s="64"/>
+      <c r="CG79" s="64"/>
+      <c r="CH79" s="64"/>
+      <c r="CI79" s="64"/>
+      <c r="CJ79" s="64"/>
+      <c r="CK79" s="64"/>
+      <c r="CL79" s="64"/>
+      <c r="CM79" s="64"/>
+      <c r="CN79" s="64"/>
+      <c r="CO79" s="64"/>
+      <c r="CP79" s="64"/>
+      <c r="CQ79" s="64"/>
+      <c r="CR79" s="64"/>
+      <c r="CS79" s="64"/>
+      <c r="CT79" s="64"/>
+      <c r="CU79" s="64"/>
+      <c r="CV79" s="64"/>
+      <c r="CW79" s="64"/>
+      <c r="CX79" s="64"/>
+      <c r="CY79" s="64"/>
+      <c r="CZ79" s="64"/>
+      <c r="DA79" s="64"/>
+      <c r="DB79" s="64"/>
+      <c r="DC79" s="64"/>
+      <c r="DD79" s="64"/>
+      <c r="DE79" s="64"/>
+      <c r="DF79" s="64"/>
+      <c r="DG79" s="64"/>
+      <c r="DH79" s="64"/>
+      <c r="DI79" s="64"/>
+      <c r="DJ79" s="64"/>
+      <c r="DK79" s="64"/>
+      <c r="DL79" s="64"/>
+      <c r="DM79" s="64"/>
+      <c r="DN79" s="64"/>
+      <c r="DO79" s="64"/>
+      <c r="DP79" s="64"/>
+      <c r="DQ79" s="64"/>
+      <c r="DR79" s="64"/>
+      <c r="DS79" s="64"/>
+      <c r="DT79" s="64"/>
+      <c r="DU79" s="64"/>
+      <c r="DV79" s="64"/>
+      <c r="DW79" s="64"/>
+      <c r="DX79" s="64"/>
+      <c r="DY79" s="64"/>
+      <c r="DZ79" s="64"/>
+      <c r="EA79" s="64"/>
+      <c r="EB79" s="64"/>
+      <c r="EC79" s="64"/>
+      <c r="ED79" s="64"/>
+      <c r="EE79" s="64"/>
+      <c r="EF79" s="64"/>
+      <c r="EG79" s="64"/>
+      <c r="EH79" s="64"/>
     </row>
     <row r="80" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A80" s="55" t="s">
+      <c r="A80" s="65" t="s">
         <v>160</v>
       </c>
-      <c r="B80" s="56" t="s">
+      <c r="B80" s="58" t="s">
         <v>161</v>
       </c>
-      <c r="C80" s="57" t="s">
+      <c r="C80" s="66" t="s">
         <v>86</v>
       </c>
       <c r="D80" s="9" t="s">
@@ -44023,14 +44023,18 @@
       </c>
     </row>
     <row r="81" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A81" s="55"/>
-      <c r="B81" s="55"/>
-      <c r="C81" s="55"/>
+      <c r="A81" s="65"/>
+      <c r="B81" s="65"/>
+      <c r="C81" s="65"/>
       <c r="D81" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="E81" s="10"/>
-      <c r="F81" s="10"/>
+      <c r="E81" s="10">
+        <v>46308</v>
+      </c>
+      <c r="F81" s="10">
+        <v>46308</v>
+      </c>
       <c r="G81" s="13" t="str">
         <f t="shared" si="91"/>
         <v/>
@@ -44325,7 +44329,7 @@
       </c>
       <c r="CB81" s="13" t="str">
         <f t="shared" si="98"/>
-        <v/>
+        <v>▪</v>
       </c>
       <c r="CC81" s="13" t="str">
         <f t="shared" si="98"/>
@@ -44561,13 +44565,13 @@
       </c>
     </row>
     <row r="82" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A82" s="55" t="s">
+      <c r="A82" s="65" t="s">
         <v>162</v>
       </c>
-      <c r="B82" s="56" t="s">
+      <c r="B82" s="58" t="s">
         <v>163</v>
       </c>
-      <c r="C82" s="57" t="s">
+      <c r="C82" s="66" t="s">
         <v>86</v>
       </c>
       <c r="D82" s="9" t="s">
@@ -45109,14 +45113,18 @@
       </c>
     </row>
     <row r="83" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A83" s="55"/>
-      <c r="B83" s="55"/>
-      <c r="C83" s="55"/>
+      <c r="A83" s="65"/>
+      <c r="B83" s="65"/>
+      <c r="C83" s="65"/>
       <c r="D83" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="E83" s="10"/>
-      <c r="F83" s="10"/>
+      <c r="E83" s="10">
+        <v>46309</v>
+      </c>
+      <c r="F83" s="10">
+        <v>46326</v>
+      </c>
       <c r="G83" s="13" t="str">
         <f t="shared" si="91"/>
         <v/>
@@ -45415,75 +45423,75 @@
       </c>
       <c r="CC83" s="13" t="str">
         <f t="shared" si="98"/>
-        <v/>
+        <v>▪</v>
       </c>
       <c r="CD83" s="13" t="str">
         <f t="shared" si="98"/>
-        <v/>
+        <v>▪</v>
       </c>
       <c r="CE83" s="13" t="str">
         <f t="shared" si="98"/>
-        <v/>
+        <v>▪</v>
       </c>
       <c r="CF83" s="13" t="str">
         <f t="shared" si="98"/>
-        <v/>
+        <v>▪</v>
       </c>
       <c r="CG83" s="13" t="str">
         <f t="shared" si="98"/>
-        <v/>
+        <v>▪</v>
       </c>
       <c r="CH83" s="13" t="str">
         <f t="shared" si="98"/>
-        <v/>
+        <v>▪</v>
       </c>
       <c r="CI83" s="13" t="str">
         <f t="shared" si="99"/>
-        <v/>
+        <v>▪</v>
       </c>
       <c r="CJ83" s="13" t="str">
         <f t="shared" si="99"/>
-        <v/>
+        <v>▪</v>
       </c>
       <c r="CK83" s="13" t="str">
         <f t="shared" si="99"/>
-        <v/>
+        <v>▪</v>
       </c>
       <c r="CL83" s="13" t="str">
         <f t="shared" si="99"/>
-        <v/>
+        <v>▪</v>
       </c>
       <c r="CM83" s="13" t="str">
         <f t="shared" si="99"/>
-        <v/>
+        <v>▪</v>
       </c>
       <c r="CN83" s="13" t="str">
         <f t="shared" si="99"/>
-        <v/>
+        <v>▪</v>
       </c>
       <c r="CO83" s="13" t="str">
         <f t="shared" si="99"/>
-        <v/>
+        <v>▪</v>
       </c>
       <c r="CP83" s="13" t="str">
         <f t="shared" si="99"/>
-        <v/>
+        <v>▪</v>
       </c>
       <c r="CQ83" s="13" t="str">
         <f t="shared" si="99"/>
-        <v/>
+        <v>▪</v>
       </c>
       <c r="CR83" s="13" t="str">
         <f t="shared" si="99"/>
-        <v/>
+        <v>▪</v>
       </c>
       <c r="CS83" s="13" t="str">
         <f t="shared" si="100"/>
-        <v/>
+        <v>▪</v>
       </c>
       <c r="CT83" s="13" t="str">
         <f t="shared" si="100"/>
-        <v/>
+        <v>▪</v>
       </c>
       <c r="CU83" s="13" t="str">
         <f t="shared" si="100"/>
@@ -45647,13 +45655,13 @@
       </c>
     </row>
     <row r="84" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A84" s="55" t="s">
+      <c r="A84" s="65" t="s">
         <v>164</v>
       </c>
-      <c r="B84" s="56" t="s">
+      <c r="B84" s="58" t="s">
         <v>165</v>
       </c>
-      <c r="C84" s="57" t="s">
+      <c r="C84" s="66" t="s">
         <v>86</v>
       </c>
       <c r="D84" s="9" t="s">
@@ -46195,9 +46203,9 @@
       </c>
     </row>
     <row r="85" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A85" s="55"/>
-      <c r="B85" s="55"/>
-      <c r="C85" s="55"/>
+      <c r="A85" s="65"/>
+      <c r="B85" s="65"/>
+      <c r="C85" s="65"/>
       <c r="D85" s="12" t="s">
         <v>80</v>
       </c>
@@ -46735,13 +46743,13 @@
       </c>
     </row>
     <row r="86" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A86" s="55" t="s">
+      <c r="A86" s="65" t="s">
         <v>166</v>
       </c>
-      <c r="B86" s="56" t="s">
+      <c r="B86" s="58" t="s">
         <v>167</v>
       </c>
-      <c r="C86" s="57" t="s">
+      <c r="C86" s="66" t="s">
         <v>86</v>
       </c>
       <c r="D86" s="9" t="s">
@@ -47283,9 +47291,9 @@
       </c>
     </row>
     <row r="87" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A87" s="55"/>
-      <c r="B87" s="55"/>
-      <c r="C87" s="55"/>
+      <c r="A87" s="65"/>
+      <c r="B87" s="65"/>
+      <c r="C87" s="65"/>
       <c r="D87" s="12" t="s">
         <v>80</v>
       </c>
@@ -47821,13 +47829,13 @@
       </c>
     </row>
     <row r="88" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A88" s="55" t="s">
+      <c r="A88" s="65" t="s">
         <v>168</v>
       </c>
-      <c r="B88" s="56" t="s">
+      <c r="B88" s="58" t="s">
         <v>169</v>
       </c>
-      <c r="C88" s="57" t="s">
+      <c r="C88" s="66" t="s">
         <v>86</v>
       </c>
       <c r="D88" s="9" t="s">
@@ -48369,13 +48377,15 @@
       </c>
     </row>
     <row r="89" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A89" s="55"/>
-      <c r="B89" s="55"/>
-      <c r="C89" s="55"/>
+      <c r="A89" s="65"/>
+      <c r="B89" s="65"/>
+      <c r="C89" s="65"/>
       <c r="D89" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="E89" s="10"/>
+      <c r="E89" s="10">
+        <v>46298</v>
+      </c>
       <c r="F89" s="10"/>
       <c r="G89" s="13" t="str">
         <f t="shared" si="91"/>
@@ -48907,13 +48917,13 @@
       </c>
     </row>
     <row r="90" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A90" s="55" t="s">
+      <c r="A90" s="65" t="s">
         <v>170</v>
       </c>
-      <c r="B90" s="56" t="s">
+      <c r="B90" s="58" t="s">
         <v>171</v>
       </c>
-      <c r="C90" s="57" t="s">
+      <c r="C90" s="66" t="s">
         <v>78</v>
       </c>
       <c r="D90" s="9" t="s">
@@ -49455,9 +49465,9 @@
       </c>
     </row>
     <row r="91" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A91" s="55"/>
-      <c r="B91" s="55"/>
-      <c r="C91" s="55"/>
+      <c r="A91" s="65"/>
+      <c r="B91" s="65"/>
+      <c r="C91" s="65"/>
       <c r="D91" s="12" t="s">
         <v>80</v>
       </c>
@@ -49993,155 +50003,155 @@
       </c>
     </row>
     <row r="92" spans="1:138" ht="15.75" customHeight="1">
-      <c r="A92" s="54" t="s">
+      <c r="A92" s="64" t="s">
         <v>172</v>
       </c>
-      <c r="B92" s="54"/>
-      <c r="C92" s="54"/>
-      <c r="D92" s="54"/>
-      <c r="E92" s="54"/>
-      <c r="F92" s="54"/>
-      <c r="G92" s="54"/>
-      <c r="H92" s="54"/>
-      <c r="I92" s="54"/>
-      <c r="J92" s="54"/>
-      <c r="K92" s="54"/>
-      <c r="L92" s="54"/>
-      <c r="M92" s="54"/>
-      <c r="N92" s="54"/>
-      <c r="O92" s="54"/>
-      <c r="P92" s="54"/>
-      <c r="Q92" s="54"/>
-      <c r="R92" s="54"/>
-      <c r="S92" s="54"/>
-      <c r="T92" s="54"/>
-      <c r="U92" s="54"/>
-      <c r="V92" s="54"/>
-      <c r="W92" s="54"/>
-      <c r="X92" s="54"/>
-      <c r="Y92" s="54"/>
-      <c r="Z92" s="54"/>
-      <c r="AA92" s="54"/>
-      <c r="AB92" s="54"/>
-      <c r="AC92" s="54"/>
-      <c r="AD92" s="54"/>
-      <c r="AE92" s="54"/>
-      <c r="AF92" s="54"/>
-      <c r="AG92" s="54"/>
-      <c r="AH92" s="54"/>
-      <c r="AI92" s="54"/>
-      <c r="AJ92" s="54"/>
-      <c r="AK92" s="54"/>
-      <c r="AL92" s="54"/>
-      <c r="AM92" s="54"/>
-      <c r="AN92" s="54"/>
-      <c r="AO92" s="54"/>
-      <c r="AP92" s="54"/>
-      <c r="AQ92" s="54"/>
-      <c r="AR92" s="54"/>
-      <c r="AS92" s="54"/>
-      <c r="AT92" s="54"/>
-      <c r="AU92" s="54"/>
-      <c r="AV92" s="54"/>
-      <c r="AW92" s="54"/>
-      <c r="AX92" s="54"/>
-      <c r="AY92" s="54"/>
-      <c r="AZ92" s="54"/>
-      <c r="BA92" s="54"/>
-      <c r="BB92" s="54"/>
-      <c r="BC92" s="54"/>
-      <c r="BD92" s="54"/>
-      <c r="BE92" s="54"/>
-      <c r="BF92" s="54"/>
-      <c r="BG92" s="54"/>
-      <c r="BH92" s="54"/>
-      <c r="BI92" s="54"/>
-      <c r="BJ92" s="54"/>
-      <c r="BK92" s="54"/>
-      <c r="BL92" s="54"/>
-      <c r="BM92" s="54"/>
-      <c r="BN92" s="54"/>
-      <c r="BO92" s="54"/>
-      <c r="BP92" s="54"/>
-      <c r="BQ92" s="54"/>
-      <c r="BR92" s="54"/>
-      <c r="BS92" s="54"/>
-      <c r="BT92" s="54"/>
-      <c r="BU92" s="54"/>
-      <c r="BV92" s="54"/>
-      <c r="BW92" s="54"/>
-      <c r="BX92" s="54"/>
-      <c r="BY92" s="54"/>
-      <c r="BZ92" s="54"/>
-      <c r="CA92" s="54"/>
-      <c r="CB92" s="54"/>
-      <c r="CC92" s="54"/>
-      <c r="CD92" s="54"/>
-      <c r="CE92" s="54"/>
-      <c r="CF92" s="54"/>
-      <c r="CG92" s="54"/>
-      <c r="CH92" s="54"/>
-      <c r="CI92" s="54"/>
-      <c r="CJ92" s="54"/>
-      <c r="CK92" s="54"/>
-      <c r="CL92" s="54"/>
-      <c r="CM92" s="54"/>
-      <c r="CN92" s="54"/>
-      <c r="CO92" s="54"/>
-      <c r="CP92" s="54"/>
-      <c r="CQ92" s="54"/>
-      <c r="CR92" s="54"/>
-      <c r="CS92" s="54"/>
-      <c r="CT92" s="54"/>
-      <c r="CU92" s="54"/>
-      <c r="CV92" s="54"/>
-      <c r="CW92" s="54"/>
-      <c r="CX92" s="54"/>
-      <c r="CY92" s="54"/>
-      <c r="CZ92" s="54"/>
-      <c r="DA92" s="54"/>
-      <c r="DB92" s="54"/>
-      <c r="DC92" s="54"/>
-      <c r="DD92" s="54"/>
-      <c r="DE92" s="54"/>
-      <c r="DF92" s="54"/>
-      <c r="DG92" s="54"/>
-      <c r="DH92" s="54"/>
-      <c r="DI92" s="54"/>
-      <c r="DJ92" s="54"/>
-      <c r="DK92" s="54"/>
-      <c r="DL92" s="54"/>
-      <c r="DM92" s="54"/>
-      <c r="DN92" s="54"/>
-      <c r="DO92" s="54"/>
-      <c r="DP92" s="54"/>
-      <c r="DQ92" s="54"/>
-      <c r="DR92" s="54"/>
-      <c r="DS92" s="54"/>
-      <c r="DT92" s="54"/>
-      <c r="DU92" s="54"/>
-      <c r="DV92" s="54"/>
-      <c r="DW92" s="54"/>
-      <c r="DX92" s="54"/>
-      <c r="DY92" s="54"/>
-      <c r="DZ92" s="54"/>
-      <c r="EA92" s="54"/>
-      <c r="EB92" s="54"/>
-      <c r="EC92" s="54"/>
-      <c r="ED92" s="54"/>
-      <c r="EE92" s="54"/>
-      <c r="EF92" s="54"/>
-      <c r="EG92" s="54"/>
-      <c r="EH92" s="54"/>
+      <c r="B92" s="64"/>
+      <c r="C92" s="64"/>
+      <c r="D92" s="64"/>
+      <c r="E92" s="64"/>
+      <c r="F92" s="64"/>
+      <c r="G92" s="64"/>
+      <c r="H92" s="64"/>
+      <c r="I92" s="64"/>
+      <c r="J92" s="64"/>
+      <c r="K92" s="64"/>
+      <c r="L92" s="64"/>
+      <c r="M92" s="64"/>
+      <c r="N92" s="64"/>
+      <c r="O92" s="64"/>
+      <c r="P92" s="64"/>
+      <c r="Q92" s="64"/>
+      <c r="R92" s="64"/>
+      <c r="S92" s="64"/>
+      <c r="T92" s="64"/>
+      <c r="U92" s="64"/>
+      <c r="V92" s="64"/>
+      <c r="W92" s="64"/>
+      <c r="X92" s="64"/>
+      <c r="Y92" s="64"/>
+      <c r="Z92" s="64"/>
+      <c r="AA92" s="64"/>
+      <c r="AB92" s="64"/>
+      <c r="AC92" s="64"/>
+      <c r="AD92" s="64"/>
+      <c r="AE92" s="64"/>
+      <c r="AF92" s="64"/>
+      <c r="AG92" s="64"/>
+      <c r="AH92" s="64"/>
+      <c r="AI92" s="64"/>
+      <c r="AJ92" s="64"/>
+      <c r="AK92" s="64"/>
+      <c r="AL92" s="64"/>
+      <c r="AM92" s="64"/>
+      <c r="AN92" s="64"/>
+      <c r="AO92" s="64"/>
+      <c r="AP92" s="64"/>
+      <c r="AQ92" s="64"/>
+      <c r="AR92" s="64"/>
+      <c r="AS92" s="64"/>
+      <c r="AT92" s="64"/>
+      <c r="AU92" s="64"/>
+      <c r="AV92" s="64"/>
+      <c r="AW92" s="64"/>
+      <c r="AX92" s="64"/>
+      <c r="AY92" s="64"/>
+      <c r="AZ92" s="64"/>
+      <c r="BA92" s="64"/>
+      <c r="BB92" s="64"/>
+      <c r="BC92" s="64"/>
+      <c r="BD92" s="64"/>
+      <c r="BE92" s="64"/>
+      <c r="BF92" s="64"/>
+      <c r="BG92" s="64"/>
+      <c r="BH92" s="64"/>
+      <c r="BI92" s="64"/>
+      <c r="BJ92" s="64"/>
+      <c r="BK92" s="64"/>
+      <c r="BL92" s="64"/>
+      <c r="BM92" s="64"/>
+      <c r="BN92" s="64"/>
+      <c r="BO92" s="64"/>
+      <c r="BP92" s="64"/>
+      <c r="BQ92" s="64"/>
+      <c r="BR92" s="64"/>
+      <c r="BS92" s="64"/>
+      <c r="BT92" s="64"/>
+      <c r="BU92" s="64"/>
+      <c r="BV92" s="64"/>
+      <c r="BW92" s="64"/>
+      <c r="BX92" s="64"/>
+      <c r="BY92" s="64"/>
+      <c r="BZ92" s="64"/>
+      <c r="CA92" s="64"/>
+      <c r="CB92" s="64"/>
+      <c r="CC92" s="64"/>
+      <c r="CD92" s="64"/>
+      <c r="CE92" s="64"/>
+      <c r="CF92" s="64"/>
+      <c r="CG92" s="64"/>
+      <c r="CH92" s="64"/>
+      <c r="CI92" s="64"/>
+      <c r="CJ92" s="64"/>
+      <c r="CK92" s="64"/>
+      <c r="CL92" s="64"/>
+      <c r="CM92" s="64"/>
+      <c r="CN92" s="64"/>
+      <c r="CO92" s="64"/>
+      <c r="CP92" s="64"/>
+      <c r="CQ92" s="64"/>
+      <c r="CR92" s="64"/>
+      <c r="CS92" s="64"/>
+      <c r="CT92" s="64"/>
+      <c r="CU92" s="64"/>
+      <c r="CV92" s="64"/>
+      <c r="CW92" s="64"/>
+      <c r="CX92" s="64"/>
+      <c r="CY92" s="64"/>
+      <c r="CZ92" s="64"/>
+      <c r="DA92" s="64"/>
+      <c r="DB92" s="64"/>
+      <c r="DC92" s="64"/>
+      <c r="DD92" s="64"/>
+      <c r="DE92" s="64"/>
+      <c r="DF92" s="64"/>
+      <c r="DG92" s="64"/>
+      <c r="DH92" s="64"/>
+      <c r="DI92" s="64"/>
+      <c r="DJ92" s="64"/>
+      <c r="DK92" s="64"/>
+      <c r="DL92" s="64"/>
+      <c r="DM92" s="64"/>
+      <c r="DN92" s="64"/>
+      <c r="DO92" s="64"/>
+      <c r="DP92" s="64"/>
+      <c r="DQ92" s="64"/>
+      <c r="DR92" s="64"/>
+      <c r="DS92" s="64"/>
+      <c r="DT92" s="64"/>
+      <c r="DU92" s="64"/>
+      <c r="DV92" s="64"/>
+      <c r="DW92" s="64"/>
+      <c r="DX92" s="64"/>
+      <c r="DY92" s="64"/>
+      <c r="DZ92" s="64"/>
+      <c r="EA92" s="64"/>
+      <c r="EB92" s="64"/>
+      <c r="EC92" s="64"/>
+      <c r="ED92" s="64"/>
+      <c r="EE92" s="64"/>
+      <c r="EF92" s="64"/>
+      <c r="EG92" s="64"/>
+      <c r="EH92" s="64"/>
     </row>
     <row r="93" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A93" s="55" t="s">
+      <c r="A93" s="65" t="s">
         <v>173</v>
       </c>
-      <c r="B93" s="56" t="s">
+      <c r="B93" s="58" t="s">
         <v>174</v>
       </c>
-      <c r="C93" s="57" t="s">
+      <c r="C93" s="66" t="s">
         <v>78</v>
       </c>
       <c r="D93" s="9" t="s">
@@ -50683,9 +50693,9 @@
       </c>
     </row>
     <row r="94" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A94" s="55"/>
-      <c r="B94" s="55"/>
-      <c r="C94" s="55"/>
+      <c r="A94" s="65"/>
+      <c r="B94" s="65"/>
+      <c r="C94" s="65"/>
       <c r="D94" s="12" t="s">
         <v>80</v>
       </c>
@@ -51221,13 +51231,13 @@
       </c>
     </row>
     <row r="95" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A95" s="55" t="s">
+      <c r="A95" s="65" t="s">
         <v>175</v>
       </c>
-      <c r="B95" s="56" t="s">
+      <c r="B95" s="58" t="s">
         <v>176</v>
       </c>
-      <c r="C95" s="57" t="s">
+      <c r="C95" s="66" t="s">
         <v>86</v>
       </c>
       <c r="D95" s="9" t="s">
@@ -51769,9 +51779,9 @@
       </c>
     </row>
     <row r="96" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A96" s="55"/>
-      <c r="B96" s="55"/>
-      <c r="C96" s="55"/>
+      <c r="A96" s="65"/>
+      <c r="B96" s="65"/>
+      <c r="C96" s="65"/>
       <c r="D96" s="12" t="s">
         <v>80</v>
       </c>
@@ -52307,13 +52317,13 @@
       </c>
     </row>
     <row r="97" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A97" s="55" t="s">
+      <c r="A97" s="65" t="s">
         <v>177</v>
       </c>
-      <c r="B97" s="56" t="s">
+      <c r="B97" s="58" t="s">
         <v>178</v>
       </c>
-      <c r="C97" s="57" t="s">
+      <c r="C97" s="66" t="s">
         <v>78</v>
       </c>
       <c r="D97" s="9" t="s">
@@ -52855,9 +52865,9 @@
       </c>
     </row>
     <row r="98" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A98" s="55"/>
-      <c r="B98" s="55"/>
-      <c r="C98" s="55"/>
+      <c r="A98" s="65"/>
+      <c r="B98" s="65"/>
+      <c r="C98" s="65"/>
       <c r="D98" s="12" t="s">
         <v>80</v>
       </c>
@@ -53393,155 +53403,155 @@
       </c>
     </row>
     <row r="99" spans="1:138" ht="15.75" customHeight="1">
-      <c r="A99" s="54" t="s">
+      <c r="A99" s="64" t="s">
         <v>179</v>
       </c>
-      <c r="B99" s="54"/>
-      <c r="C99" s="54"/>
-      <c r="D99" s="54"/>
-      <c r="E99" s="54"/>
-      <c r="F99" s="54"/>
-      <c r="G99" s="54"/>
-      <c r="H99" s="54"/>
-      <c r="I99" s="54"/>
-      <c r="J99" s="54"/>
-      <c r="K99" s="54"/>
-      <c r="L99" s="54"/>
-      <c r="M99" s="54"/>
-      <c r="N99" s="54"/>
-      <c r="O99" s="54"/>
-      <c r="P99" s="54"/>
-      <c r="Q99" s="54"/>
-      <c r="R99" s="54"/>
-      <c r="S99" s="54"/>
-      <c r="T99" s="54"/>
-      <c r="U99" s="54"/>
-      <c r="V99" s="54"/>
-      <c r="W99" s="54"/>
-      <c r="X99" s="54"/>
-      <c r="Y99" s="54"/>
-      <c r="Z99" s="54"/>
-      <c r="AA99" s="54"/>
-      <c r="AB99" s="54"/>
-      <c r="AC99" s="54"/>
-      <c r="AD99" s="54"/>
-      <c r="AE99" s="54"/>
-      <c r="AF99" s="54"/>
-      <c r="AG99" s="54"/>
-      <c r="AH99" s="54"/>
-      <c r="AI99" s="54"/>
-      <c r="AJ99" s="54"/>
-      <c r="AK99" s="54"/>
-      <c r="AL99" s="54"/>
-      <c r="AM99" s="54"/>
-      <c r="AN99" s="54"/>
-      <c r="AO99" s="54"/>
-      <c r="AP99" s="54"/>
-      <c r="AQ99" s="54"/>
-      <c r="AR99" s="54"/>
-      <c r="AS99" s="54"/>
-      <c r="AT99" s="54"/>
-      <c r="AU99" s="54"/>
-      <c r="AV99" s="54"/>
-      <c r="AW99" s="54"/>
-      <c r="AX99" s="54"/>
-      <c r="AY99" s="54"/>
-      <c r="AZ99" s="54"/>
-      <c r="BA99" s="54"/>
-      <c r="BB99" s="54"/>
-      <c r="BC99" s="54"/>
-      <c r="BD99" s="54"/>
-      <c r="BE99" s="54"/>
-      <c r="BF99" s="54"/>
-      <c r="BG99" s="54"/>
-      <c r="BH99" s="54"/>
-      <c r="BI99" s="54"/>
-      <c r="BJ99" s="54"/>
-      <c r="BK99" s="54"/>
-      <c r="BL99" s="54"/>
-      <c r="BM99" s="54"/>
-      <c r="BN99" s="54"/>
-      <c r="BO99" s="54"/>
-      <c r="BP99" s="54"/>
-      <c r="BQ99" s="54"/>
-      <c r="BR99" s="54"/>
-      <c r="BS99" s="54"/>
-      <c r="BT99" s="54"/>
-      <c r="BU99" s="54"/>
-      <c r="BV99" s="54"/>
-      <c r="BW99" s="54"/>
-      <c r="BX99" s="54"/>
-      <c r="BY99" s="54"/>
-      <c r="BZ99" s="54"/>
-      <c r="CA99" s="54"/>
-      <c r="CB99" s="54"/>
-      <c r="CC99" s="54"/>
-      <c r="CD99" s="54"/>
-      <c r="CE99" s="54"/>
-      <c r="CF99" s="54"/>
-      <c r="CG99" s="54"/>
-      <c r="CH99" s="54"/>
-      <c r="CI99" s="54"/>
-      <c r="CJ99" s="54"/>
-      <c r="CK99" s="54"/>
-      <c r="CL99" s="54"/>
-      <c r="CM99" s="54"/>
-      <c r="CN99" s="54"/>
-      <c r="CO99" s="54"/>
-      <c r="CP99" s="54"/>
-      <c r="CQ99" s="54"/>
-      <c r="CR99" s="54"/>
-      <c r="CS99" s="54"/>
-      <c r="CT99" s="54"/>
-      <c r="CU99" s="54"/>
-      <c r="CV99" s="54"/>
-      <c r="CW99" s="54"/>
-      <c r="CX99" s="54"/>
-      <c r="CY99" s="54"/>
-      <c r="CZ99" s="54"/>
-      <c r="DA99" s="54"/>
-      <c r="DB99" s="54"/>
-      <c r="DC99" s="54"/>
-      <c r="DD99" s="54"/>
-      <c r="DE99" s="54"/>
-      <c r="DF99" s="54"/>
-      <c r="DG99" s="54"/>
-      <c r="DH99" s="54"/>
-      <c r="DI99" s="54"/>
-      <c r="DJ99" s="54"/>
-      <c r="DK99" s="54"/>
-      <c r="DL99" s="54"/>
-      <c r="DM99" s="54"/>
-      <c r="DN99" s="54"/>
-      <c r="DO99" s="54"/>
-      <c r="DP99" s="54"/>
-      <c r="DQ99" s="54"/>
-      <c r="DR99" s="54"/>
-      <c r="DS99" s="54"/>
-      <c r="DT99" s="54"/>
-      <c r="DU99" s="54"/>
-      <c r="DV99" s="54"/>
-      <c r="DW99" s="54"/>
-      <c r="DX99" s="54"/>
-      <c r="DY99" s="54"/>
-      <c r="DZ99" s="54"/>
-      <c r="EA99" s="54"/>
-      <c r="EB99" s="54"/>
-      <c r="EC99" s="54"/>
-      <c r="ED99" s="54"/>
-      <c r="EE99" s="54"/>
-      <c r="EF99" s="54"/>
-      <c r="EG99" s="54"/>
-      <c r="EH99" s="54"/>
+      <c r="B99" s="64"/>
+      <c r="C99" s="64"/>
+      <c r="D99" s="64"/>
+      <c r="E99" s="64"/>
+      <c r="F99" s="64"/>
+      <c r="G99" s="64"/>
+      <c r="H99" s="64"/>
+      <c r="I99" s="64"/>
+      <c r="J99" s="64"/>
+      <c r="K99" s="64"/>
+      <c r="L99" s="64"/>
+      <c r="M99" s="64"/>
+      <c r="N99" s="64"/>
+      <c r="O99" s="64"/>
+      <c r="P99" s="64"/>
+      <c r="Q99" s="64"/>
+      <c r="R99" s="64"/>
+      <c r="S99" s="64"/>
+      <c r="T99" s="64"/>
+      <c r="U99" s="64"/>
+      <c r="V99" s="64"/>
+      <c r="W99" s="64"/>
+      <c r="X99" s="64"/>
+      <c r="Y99" s="64"/>
+      <c r="Z99" s="64"/>
+      <c r="AA99" s="64"/>
+      <c r="AB99" s="64"/>
+      <c r="AC99" s="64"/>
+      <c r="AD99" s="64"/>
+      <c r="AE99" s="64"/>
+      <c r="AF99" s="64"/>
+      <c r="AG99" s="64"/>
+      <c r="AH99" s="64"/>
+      <c r="AI99" s="64"/>
+      <c r="AJ99" s="64"/>
+      <c r="AK99" s="64"/>
+      <c r="AL99" s="64"/>
+      <c r="AM99" s="64"/>
+      <c r="AN99" s="64"/>
+      <c r="AO99" s="64"/>
+      <c r="AP99" s="64"/>
+      <c r="AQ99" s="64"/>
+      <c r="AR99" s="64"/>
+      <c r="AS99" s="64"/>
+      <c r="AT99" s="64"/>
+      <c r="AU99" s="64"/>
+      <c r="AV99" s="64"/>
+      <c r="AW99" s="64"/>
+      <c r="AX99" s="64"/>
+      <c r="AY99" s="64"/>
+      <c r="AZ99" s="64"/>
+      <c r="BA99" s="64"/>
+      <c r="BB99" s="64"/>
+      <c r="BC99" s="64"/>
+      <c r="BD99" s="64"/>
+      <c r="BE99" s="64"/>
+      <c r="BF99" s="64"/>
+      <c r="BG99" s="64"/>
+      <c r="BH99" s="64"/>
+      <c r="BI99" s="64"/>
+      <c r="BJ99" s="64"/>
+      <c r="BK99" s="64"/>
+      <c r="BL99" s="64"/>
+      <c r="BM99" s="64"/>
+      <c r="BN99" s="64"/>
+      <c r="BO99" s="64"/>
+      <c r="BP99" s="64"/>
+      <c r="BQ99" s="64"/>
+      <c r="BR99" s="64"/>
+      <c r="BS99" s="64"/>
+      <c r="BT99" s="64"/>
+      <c r="BU99" s="64"/>
+      <c r="BV99" s="64"/>
+      <c r="BW99" s="64"/>
+      <c r="BX99" s="64"/>
+      <c r="BY99" s="64"/>
+      <c r="BZ99" s="64"/>
+      <c r="CA99" s="64"/>
+      <c r="CB99" s="64"/>
+      <c r="CC99" s="64"/>
+      <c r="CD99" s="64"/>
+      <c r="CE99" s="64"/>
+      <c r="CF99" s="64"/>
+      <c r="CG99" s="64"/>
+      <c r="CH99" s="64"/>
+      <c r="CI99" s="64"/>
+      <c r="CJ99" s="64"/>
+      <c r="CK99" s="64"/>
+      <c r="CL99" s="64"/>
+      <c r="CM99" s="64"/>
+      <c r="CN99" s="64"/>
+      <c r="CO99" s="64"/>
+      <c r="CP99" s="64"/>
+      <c r="CQ99" s="64"/>
+      <c r="CR99" s="64"/>
+      <c r="CS99" s="64"/>
+      <c r="CT99" s="64"/>
+      <c r="CU99" s="64"/>
+      <c r="CV99" s="64"/>
+      <c r="CW99" s="64"/>
+      <c r="CX99" s="64"/>
+      <c r="CY99" s="64"/>
+      <c r="CZ99" s="64"/>
+      <c r="DA99" s="64"/>
+      <c r="DB99" s="64"/>
+      <c r="DC99" s="64"/>
+      <c r="DD99" s="64"/>
+      <c r="DE99" s="64"/>
+      <c r="DF99" s="64"/>
+      <c r="DG99" s="64"/>
+      <c r="DH99" s="64"/>
+      <c r="DI99" s="64"/>
+      <c r="DJ99" s="64"/>
+      <c r="DK99" s="64"/>
+      <c r="DL99" s="64"/>
+      <c r="DM99" s="64"/>
+      <c r="DN99" s="64"/>
+      <c r="DO99" s="64"/>
+      <c r="DP99" s="64"/>
+      <c r="DQ99" s="64"/>
+      <c r="DR99" s="64"/>
+      <c r="DS99" s="64"/>
+      <c r="DT99" s="64"/>
+      <c r="DU99" s="64"/>
+      <c r="DV99" s="64"/>
+      <c r="DW99" s="64"/>
+      <c r="DX99" s="64"/>
+      <c r="DY99" s="64"/>
+      <c r="DZ99" s="64"/>
+      <c r="EA99" s="64"/>
+      <c r="EB99" s="64"/>
+      <c r="EC99" s="64"/>
+      <c r="ED99" s="64"/>
+      <c r="EE99" s="64"/>
+      <c r="EF99" s="64"/>
+      <c r="EG99" s="64"/>
+      <c r="EH99" s="64"/>
     </row>
     <row r="100" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A100" s="55" t="s">
+      <c r="A100" s="65" t="s">
         <v>180</v>
       </c>
-      <c r="B100" s="56" t="s">
+      <c r="B100" s="58" t="s">
         <v>181</v>
       </c>
-      <c r="C100" s="57" t="s">
+      <c r="C100" s="66" t="s">
         <v>86</v>
       </c>
       <c r="D100" s="9" t="s">
@@ -54083,9 +54093,9 @@
       </c>
     </row>
     <row r="101" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A101" s="55"/>
-      <c r="B101" s="55"/>
-      <c r="C101" s="55"/>
+      <c r="A101" s="65"/>
+      <c r="B101" s="65"/>
+      <c r="C101" s="65"/>
       <c r="D101" s="12" t="s">
         <v>80</v>
       </c>
@@ -54621,13 +54631,13 @@
       </c>
     </row>
     <row r="102" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A102" s="55" t="s">
+      <c r="A102" s="65" t="s">
         <v>182</v>
       </c>
-      <c r="B102" s="56" t="s">
+      <c r="B102" s="58" t="s">
         <v>183</v>
       </c>
-      <c r="C102" s="57" t="s">
+      <c r="C102" s="66" t="s">
         <v>78</v>
       </c>
       <c r="D102" s="9" t="s">
@@ -55169,9 +55179,9 @@
       </c>
     </row>
     <row r="103" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A103" s="55"/>
-      <c r="B103" s="55"/>
-      <c r="C103" s="55"/>
+      <c r="A103" s="65"/>
+      <c r="B103" s="65"/>
+      <c r="C103" s="65"/>
       <c r="D103" s="12" t="s">
         <v>80</v>
       </c>
@@ -55707,13 +55717,13 @@
       </c>
     </row>
     <row r="104" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A104" s="55" t="s">
+      <c r="A104" s="65" t="s">
         <v>184</v>
       </c>
-      <c r="B104" s="56" t="s">
+      <c r="B104" s="58" t="s">
         <v>185</v>
       </c>
-      <c r="C104" s="57" t="s">
+      <c r="C104" s="66" t="s">
         <v>78</v>
       </c>
       <c r="D104" s="9" t="s">
@@ -56255,9 +56265,9 @@
       </c>
     </row>
     <row r="105" spans="1:138" ht="13.5" customHeight="1">
-      <c r="A105" s="55"/>
-      <c r="B105" s="55"/>
-      <c r="C105" s="55"/>
+      <c r="A105" s="65"/>
+      <c r="B105" s="65"/>
+      <c r="C105" s="65"/>
       <c r="D105" s="12" t="s">
         <v>80</v>
       </c>
@@ -56793,127 +56803,271 @@
       </c>
     </row>
     <row r="107" spans="1:138">
-      <c r="A107" s="58" t="s">
+      <c r="A107" s="59" t="s">
         <v>186</v>
       </c>
-      <c r="B107" s="58"/>
-      <c r="C107" s="58"/>
-      <c r="D107" s="58"/>
-      <c r="E107" s="58"/>
-      <c r="F107" s="58"/>
-      <c r="G107" s="58"/>
-      <c r="H107" s="58"/>
-      <c r="I107" s="58"/>
-      <c r="J107" s="58"/>
-      <c r="K107" s="58"/>
-      <c r="L107" s="58"/>
-      <c r="M107" s="58"/>
-      <c r="N107" s="58"/>
-      <c r="O107" s="58"/>
-      <c r="P107" s="58"/>
-      <c r="Q107" s="58"/>
-      <c r="R107" s="58"/>
-      <c r="S107" s="58"/>
-      <c r="T107" s="58"/>
+      <c r="B107" s="59"/>
+      <c r="C107" s="59"/>
+      <c r="D107" s="59"/>
+      <c r="E107" s="59"/>
+      <c r="F107" s="59"/>
+      <c r="G107" s="59"/>
+      <c r="H107" s="59"/>
+      <c r="I107" s="59"/>
+      <c r="J107" s="59"/>
+      <c r="K107" s="59"/>
+      <c r="L107" s="59"/>
+      <c r="M107" s="59"/>
+      <c r="N107" s="59"/>
+      <c r="O107" s="59"/>
+      <c r="P107" s="59"/>
+      <c r="Q107" s="59"/>
+      <c r="R107" s="59"/>
+      <c r="S107" s="59"/>
+      <c r="T107" s="59"/>
     </row>
     <row r="108" spans="1:138">
-      <c r="A108" s="59" t="s">
+      <c r="A108" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="B108" s="59"/>
-      <c r="C108" s="59"/>
-      <c r="D108" s="59"/>
-      <c r="E108" s="59"/>
-      <c r="F108" s="59"/>
-      <c r="G108" s="59"/>
-      <c r="H108" s="59"/>
-      <c r="I108" s="59"/>
-      <c r="J108" s="59"/>
-      <c r="K108" s="59"/>
-      <c r="L108" s="59"/>
-      <c r="M108" s="59"/>
-      <c r="N108" s="59"/>
-      <c r="O108" s="59"/>
-      <c r="P108" s="59"/>
-      <c r="Q108" s="59"/>
-      <c r="R108" s="59"/>
-      <c r="S108" s="59"/>
-      <c r="T108" s="59"/>
+      <c r="B108" s="60"/>
+      <c r="C108" s="60"/>
+      <c r="D108" s="60"/>
+      <c r="E108" s="60"/>
+      <c r="F108" s="60"/>
+      <c r="G108" s="60"/>
+      <c r="H108" s="60"/>
+      <c r="I108" s="60"/>
+      <c r="J108" s="60"/>
+      <c r="K108" s="60"/>
+      <c r="L108" s="60"/>
+      <c r="M108" s="60"/>
+      <c r="N108" s="60"/>
+      <c r="O108" s="60"/>
+      <c r="P108" s="60"/>
+      <c r="Q108" s="60"/>
+      <c r="R108" s="60"/>
+      <c r="S108" s="60"/>
+      <c r="T108" s="60"/>
     </row>
     <row r="109" spans="1:138">
-      <c r="A109" s="60" t="s">
+      <c r="A109" s="61" t="s">
         <v>188</v>
       </c>
-      <c r="B109" s="60"/>
-      <c r="C109" s="60"/>
-      <c r="D109" s="60"/>
-      <c r="E109" s="60"/>
-      <c r="F109" s="60"/>
-      <c r="G109" s="60"/>
-      <c r="H109" s="60"/>
-      <c r="I109" s="60"/>
-      <c r="J109" s="60"/>
-      <c r="K109" s="60"/>
-      <c r="L109" s="60"/>
-      <c r="M109" s="60"/>
-      <c r="N109" s="60"/>
-      <c r="O109" s="60"/>
-      <c r="P109" s="60"/>
-      <c r="Q109" s="60"/>
-      <c r="R109" s="60"/>
-      <c r="S109" s="60"/>
-      <c r="T109" s="60"/>
+      <c r="B109" s="61"/>
+      <c r="C109" s="61"/>
+      <c r="D109" s="61"/>
+      <c r="E109" s="61"/>
+      <c r="F109" s="61"/>
+      <c r="G109" s="61"/>
+      <c r="H109" s="61"/>
+      <c r="I109" s="61"/>
+      <c r="J109" s="61"/>
+      <c r="K109" s="61"/>
+      <c r="L109" s="61"/>
+      <c r="M109" s="61"/>
+      <c r="N109" s="61"/>
+      <c r="O109" s="61"/>
+      <c r="P109" s="61"/>
+      <c r="Q109" s="61"/>
+      <c r="R109" s="61"/>
+      <c r="S109" s="61"/>
+      <c r="T109" s="61"/>
     </row>
     <row r="110" spans="1:138">
-      <c r="A110" s="61" t="s">
+      <c r="A110" s="62" t="s">
         <v>189</v>
       </c>
-      <c r="B110" s="61"/>
-      <c r="C110" s="61"/>
-      <c r="D110" s="61"/>
-      <c r="E110" s="61"/>
-      <c r="F110" s="61"/>
-      <c r="G110" s="61"/>
-      <c r="H110" s="61"/>
-      <c r="I110" s="61"/>
-      <c r="J110" s="61"/>
-      <c r="K110" s="61"/>
-      <c r="L110" s="61"/>
-      <c r="M110" s="61"/>
-      <c r="N110" s="61"/>
-      <c r="O110" s="61"/>
-      <c r="P110" s="61"/>
-      <c r="Q110" s="61"/>
-      <c r="R110" s="61"/>
-      <c r="S110" s="61"/>
-      <c r="T110" s="61"/>
+      <c r="B110" s="62"/>
+      <c r="C110" s="62"/>
+      <c r="D110" s="62"/>
+      <c r="E110" s="62"/>
+      <c r="F110" s="62"/>
+      <c r="G110" s="62"/>
+      <c r="H110" s="62"/>
+      <c r="I110" s="62"/>
+      <c r="J110" s="62"/>
+      <c r="K110" s="62"/>
+      <c r="L110" s="62"/>
+      <c r="M110" s="62"/>
+      <c r="N110" s="62"/>
+      <c r="O110" s="62"/>
+      <c r="P110" s="62"/>
+      <c r="Q110" s="62"/>
+      <c r="R110" s="62"/>
+      <c r="S110" s="62"/>
+      <c r="T110" s="62"/>
     </row>
     <row r="111" spans="1:138">
-      <c r="A111" s="62" t="s">
+      <c r="A111" s="63" t="s">
         <v>190</v>
       </c>
-      <c r="B111" s="62"/>
-      <c r="C111" s="62"/>
-      <c r="D111" s="62"/>
-      <c r="E111" s="62"/>
-      <c r="F111" s="62"/>
-      <c r="G111" s="62"/>
-      <c r="H111" s="62"/>
-      <c r="I111" s="62"/>
-      <c r="J111" s="62"/>
-      <c r="K111" s="62"/>
-      <c r="L111" s="62"/>
-      <c r="M111" s="62"/>
-      <c r="N111" s="62"/>
-      <c r="O111" s="62"/>
-      <c r="P111" s="62"/>
-      <c r="Q111" s="62"/>
-      <c r="R111" s="62"/>
-      <c r="S111" s="62"/>
-      <c r="T111" s="62"/>
+      <c r="B111" s="63"/>
+      <c r="C111" s="63"/>
+      <c r="D111" s="63"/>
+      <c r="E111" s="63"/>
+      <c r="F111" s="63"/>
+      <c r="G111" s="63"/>
+      <c r="H111" s="63"/>
+      <c r="I111" s="63"/>
+      <c r="J111" s="63"/>
+      <c r="K111" s="63"/>
+      <c r="L111" s="63"/>
+      <c r="M111" s="63"/>
+      <c r="N111" s="63"/>
+      <c r="O111" s="63"/>
+      <c r="P111" s="63"/>
+      <c r="Q111" s="63"/>
+      <c r="R111" s="63"/>
+      <c r="S111" s="63"/>
+      <c r="T111" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="159">
+    <mergeCell ref="A1:EH1"/>
+    <mergeCell ref="G2:AK2"/>
+    <mergeCell ref="AL2:BO2"/>
+    <mergeCell ref="BP2:CT2"/>
+    <mergeCell ref="CU2:DX2"/>
+    <mergeCell ref="DY2:EH2"/>
+    <mergeCell ref="A4:EH4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="A11:EH11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="A20:EH20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="A35:EH35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="A42:EH42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="A55:EH55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="A68:EH68"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="A79:EH79"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="A92:EH92"/>
+    <mergeCell ref="A93:A94"/>
+    <mergeCell ref="B93:B94"/>
+    <mergeCell ref="C93:C94"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="C97:C98"/>
     <mergeCell ref="A107:T107"/>
     <mergeCell ref="A108:T108"/>
     <mergeCell ref="A109:T109"/>
@@ -56929,150 +57083,6 @@
     <mergeCell ref="A104:A105"/>
     <mergeCell ref="B104:B105"/>
     <mergeCell ref="C104:C105"/>
-    <mergeCell ref="A92:EH92"/>
-    <mergeCell ref="A93:A94"/>
-    <mergeCell ref="B93:B94"/>
-    <mergeCell ref="C93:C94"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="A97:A98"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="C97:C98"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="A79:EH79"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="A68:EH68"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="A55:EH55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A42:EH42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="A35:EH35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="A20:EH20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="A11:EH11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A1:EH1"/>
-    <mergeCell ref="G2:AK2"/>
-    <mergeCell ref="AL2:BO2"/>
-    <mergeCell ref="BP2:CT2"/>
-    <mergeCell ref="CU2:DX2"/>
-    <mergeCell ref="DY2:EH2"/>
-    <mergeCell ref="A4:EH4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:EH5">
     <cfRule type="cellIs" dxfId="104" priority="2" operator="equal">
@@ -57554,16 +57564,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="53" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
     </row>
     <row r="2" spans="1:8" ht="6" customHeight="1">
       <c r="A2" s="76"/>
@@ -58749,11 +58759,11 @@
       </c>
       <c r="G39" s="17" t="str">
         <f>IF(AND(Cronograma!E81&lt;&gt;"",Cronograma!F81&lt;&gt;""),"Sim","Não")</f>
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="H39" s="7" t="str">
         <f>IF(AND(Cronograma!F81&lt;&gt;"",Cronograma!F80&lt;&gt;""),IF(Cronograma!F81&gt;Cronograma!F80,"⚠ Atrasado",IF(Cronograma!F81&lt;Cronograma!F80,"✓ Adiantado","✓ No prazo")),"– Pendente")</f>
-        <v>– Pendente</v>
+        <v>✓ Adiantado</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -58782,11 +58792,11 @@
       </c>
       <c r="G40" s="17" t="str">
         <f>IF(AND(Cronograma!E83&lt;&gt;"",Cronograma!F83&lt;&gt;""),"Sim","Não")</f>
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="H40" s="7" t="str">
         <f>IF(AND(Cronograma!F83&lt;&gt;"",Cronograma!F82&lt;&gt;""),IF(Cronograma!F83&gt;Cronograma!F82,"⚠ Atrasado",IF(Cronograma!F83&lt;Cronograma!F82,"✓ Adiantado","✓ No prazo")),"– Pendente")</f>
-        <v>– Pendente</v>
+        <v>✓ Adiantado</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -59120,16 +59130,16 @@
       </c>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="65" t="s">
+      <c r="A52" s="69" t="s">
         <v>207</v>
       </c>
-      <c r="B52" s="65"/>
-      <c r="C52" s="65"/>
-      <c r="D52" s="65"/>
-      <c r="E52" s="65"/>
-      <c r="F52" s="65"/>
-      <c r="G52" s="65"/>
-      <c r="H52" s="65"/>
+      <c r="B52" s="69"/>
+      <c r="C52" s="69"/>
+      <c r="D52" s="69"/>
+      <c r="E52" s="69"/>
+      <c r="F52" s="69"/>
+      <c r="G52" s="69"/>
+      <c r="H52" s="69"/>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
@@ -59144,14 +59154,14 @@
       </c>
       <c r="E53" s="2">
         <f>COUNTIF(G5:G50,"Sim")</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>210</v>
       </c>
       <c r="H53" s="18">
         <f>IFERROR(COUNTIF(G5:G50,"Sim")/COUNTA(B5:B50),0)</f>
-        <v>0.67391304347826086</v>
+        <v>0.71739130434782605</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -59197,12 +59207,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="53" t="s">
         <v>212</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
     </row>
     <row r="2" spans="1:4" ht="6" customHeight="1">
       <c r="A2" s="76"/>
@@ -59211,120 +59221,120 @@
       <c r="D2" s="76"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="71" t="s">
         <v>213</v>
       </c>
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
     </row>
     <row r="5" spans="1:4" ht="27.75" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="67" t="s">
+      <c r="B5" s="70" t="s">
         <v>214</v>
       </c>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
     </row>
     <row r="6" spans="1:4" ht="27.75" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="70" t="s">
         <v>216</v>
       </c>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="70"/>
     </row>
     <row r="7" spans="1:4" ht="27.75" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="70" t="s">
         <v>217</v>
       </c>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
     </row>
     <row r="8" spans="1:4" ht="27.75" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B8" s="67" t="s">
+      <c r="B8" s="70" t="s">
         <v>219</v>
       </c>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="70"/>
     </row>
     <row r="9" spans="1:4" ht="27.75" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="70" t="s">
         <v>221</v>
       </c>
-      <c r="C9" s="67"/>
-      <c r="D9" s="67"/>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
     </row>
     <row r="10" spans="1:4" ht="27.75" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="70" t="s">
         <v>223</v>
       </c>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
     </row>
     <row r="11" spans="1:4" ht="27.75" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B11" s="67" t="s">
+      <c r="B11" s="70" t="s">
         <v>225</v>
       </c>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
     </row>
     <row r="12" spans="1:4" ht="27.75" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="70" t="s">
         <v>227</v>
       </c>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="70"/>
     </row>
     <row r="13" spans="1:4" ht="27.75" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="B13" s="67" t="s">
+      <c r="B13" s="70" t="s">
         <v>229</v>
       </c>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
     </row>
     <row r="14" spans="1:4" ht="27.75" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B14" s="67" t="s">
+      <c r="B14" s="70" t="s">
         <v>231</v>
       </c>
-      <c r="C14" s="67"/>
-      <c r="D14" s="67"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="70"/>
     </row>
     <row r="16" spans="1:4" ht="18" customHeight="1">
-      <c r="A16" s="66" t="s">
+      <c r="A16" s="71" t="s">
         <v>232</v>
       </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
+      <c r="B16" s="71"/>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1">
       <c r="A17" s="19" t="s">
@@ -59539,12 +59549,12 @@
       </c>
     </row>
     <row r="30" spans="1:4" ht="18" customHeight="1">
-      <c r="A30" s="66" t="s">
+      <c r="A30" s="71" t="s">
         <v>236</v>
       </c>
-      <c r="B30" s="66"/>
-      <c r="C30" s="66"/>
-      <c r="D30" s="66"/>
+      <c r="B30" s="71"/>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
     </row>
     <row r="31" spans="1:4" ht="30" customHeight="1">
       <c r="A31" s="19" t="s">
@@ -59594,21 +59604,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A30:D30"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -59629,14 +59639,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="53" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
     </row>
     <row r="2" spans="1:6" ht="6" customHeight="1">
       <c r="A2" s="76"/>
@@ -59670,13 +59680,13 @@
       <c r="A5" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="72" t="s">
         <v>249</v>
       </c>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="26" t="s">
@@ -59754,13 +59764,13 @@
       <c r="A9" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="68" t="s">
+      <c r="B9" s="72" t="s">
         <v>252</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="26" t="s">
@@ -59862,13 +59872,13 @@
       <c r="A14" s="25" t="s">
         <v>255</v>
       </c>
-      <c r="B14" s="68" t="s">
+      <c r="B14" s="72" t="s">
         <v>256</v>
       </c>
-      <c r="C14" s="68"/>
-      <c r="D14" s="68"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="68"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="26" t="s">
@@ -60042,13 +60052,13 @@
       <c r="A22" s="25" t="s">
         <v>259</v>
       </c>
-      <c r="B22" s="68" t="s">
+      <c r="B22" s="72" t="s">
         <v>260</v>
       </c>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="26" t="s">
@@ -60126,13 +60136,13 @@
       <c r="A26" s="25" t="s">
         <v>262</v>
       </c>
-      <c r="B26" s="68" t="s">
+      <c r="B26" s="72" t="s">
         <v>263</v>
       </c>
-      <c r="C26" s="68"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="68"/>
-      <c r="F26" s="68"/>
+      <c r="C26" s="72"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="72"/>
+      <c r="F26" s="72"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="26" t="s">
@@ -60282,13 +60292,13 @@
       <c r="A33" s="25" t="s">
         <v>266</v>
       </c>
-      <c r="B33" s="68" t="s">
+      <c r="B33" s="72" t="s">
         <v>267</v>
       </c>
-      <c r="C33" s="68"/>
-      <c r="D33" s="68"/>
-      <c r="E33" s="68"/>
-      <c r="F33" s="68"/>
+      <c r="C33" s="72"/>
+      <c r="D33" s="72"/>
+      <c r="E33" s="72"/>
+      <c r="F33" s="72"/>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="26" t="s">
@@ -60438,13 +60448,13 @@
       <c r="A40" s="25" t="s">
         <v>269</v>
       </c>
-      <c r="B40" s="68" t="s">
+      <c r="B40" s="72" t="s">
         <v>270</v>
       </c>
-      <c r="C40" s="68"/>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
+      <c r="C40" s="72"/>
+      <c r="D40" s="72"/>
+      <c r="E40" s="72"/>
+      <c r="F40" s="72"/>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="26" t="s">
@@ -60570,13 +60580,13 @@
       <c r="A46" s="25" t="s">
         <v>272</v>
       </c>
-      <c r="B46" s="68" t="s">
+      <c r="B46" s="72" t="s">
         <v>273</v>
       </c>
-      <c r="C46" s="68"/>
-      <c r="D46" s="68"/>
-      <c r="E46" s="68"/>
-      <c r="F46" s="68"/>
+      <c r="C46" s="72"/>
+      <c r="D46" s="72"/>
+      <c r="E46" s="72"/>
+      <c r="F46" s="72"/>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="26" t="s">
@@ -60726,13 +60736,13 @@
       <c r="A53" s="25" t="s">
         <v>278</v>
       </c>
-      <c r="B53" s="68" t="s">
+      <c r="B53" s="72" t="s">
         <v>279</v>
       </c>
-      <c r="C53" s="68"/>
-      <c r="D53" s="68"/>
-      <c r="E53" s="68"/>
-      <c r="F53" s="68"/>
+      <c r="C53" s="72"/>
+      <c r="D53" s="72"/>
+      <c r="E53" s="72"/>
+      <c r="F53" s="72"/>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="26" t="s">
@@ -60810,13 +60820,13 @@
       <c r="A57" s="25" t="s">
         <v>281</v>
       </c>
-      <c r="B57" s="68" t="s">
+      <c r="B57" s="72" t="s">
         <v>282</v>
       </c>
-      <c r="C57" s="68"/>
-      <c r="D57" s="68"/>
-      <c r="E57" s="68"/>
-      <c r="F57" s="68"/>
+      <c r="C57" s="72"/>
+      <c r="D57" s="72"/>
+      <c r="E57" s="72"/>
+      <c r="F57" s="72"/>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="26" t="s">
@@ -60891,63 +60901,63 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="18" customHeight="1">
-      <c r="A62" s="69" t="s">
+      <c r="A62" s="73" t="s">
         <v>285</v>
       </c>
-      <c r="B62" s="69"/>
-      <c r="C62" s="69"/>
-      <c r="D62" s="69"/>
-      <c r="E62" s="69"/>
-      <c r="F62" s="69"/>
+      <c r="B62" s="73"/>
+      <c r="C62" s="73"/>
+      <c r="D62" s="73"/>
+      <c r="E62" s="73"/>
+      <c r="F62" s="73"/>
     </row>
     <row r="63" spans="1:6" ht="15" customHeight="1">
-      <c r="A63" s="56" t="s">
+      <c r="A63" s="58" t="s">
         <v>286</v>
       </c>
-      <c r="B63" s="56"/>
-      <c r="C63" s="56"/>
-      <c r="D63" s="56"/>
-      <c r="E63" s="56"/>
-      <c r="F63" s="56"/>
+      <c r="B63" s="58"/>
+      <c r="C63" s="58"/>
+      <c r="D63" s="58"/>
+      <c r="E63" s="58"/>
+      <c r="F63" s="58"/>
     </row>
     <row r="64" spans="1:6" ht="15" customHeight="1">
-      <c r="A64" s="56" t="s">
+      <c r="A64" s="58" t="s">
         <v>287</v>
       </c>
-      <c r="B64" s="56"/>
-      <c r="C64" s="56"/>
-      <c r="D64" s="56"/>
-      <c r="E64" s="56"/>
-      <c r="F64" s="56"/>
+      <c r="B64" s="58"/>
+      <c r="C64" s="58"/>
+      <c r="D64" s="58"/>
+      <c r="E64" s="58"/>
+      <c r="F64" s="58"/>
     </row>
     <row r="65" spans="1:6" ht="15" customHeight="1">
-      <c r="A65" s="56" t="s">
+      <c r="A65" s="58" t="s">
         <v>288</v>
       </c>
-      <c r="B65" s="56"/>
-      <c r="C65" s="56"/>
-      <c r="D65" s="56"/>
-      <c r="E65" s="56"/>
-      <c r="F65" s="56"/>
+      <c r="B65" s="58"/>
+      <c r="C65" s="58"/>
+      <c r="D65" s="58"/>
+      <c r="E65" s="58"/>
+      <c r="F65" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B46:F46"/>
     <mergeCell ref="A65:F65"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B57:F57"/>
     <mergeCell ref="A62:F62"/>
     <mergeCell ref="A63:F63"/>
     <mergeCell ref="A64:F64"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B14:F14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -60966,14 +60976,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="53" t="s">
         <v>289</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
     </row>
     <row r="2" spans="1:6" ht="6" customHeight="1">
       <c r="A2" s="76"/>
@@ -61275,11 +61285,11 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1">
-      <c r="A18" s="71" t="s">
+      <c r="A18" s="54" t="s">
         <v>313</v>
       </c>
-      <c r="B18" s="71"/>
-      <c r="C18" s="71"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
       <c r="D18" s="32">
         <f>SUM(D5:D17)</f>
         <v>210</v>
@@ -61294,36 +61304,36 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1">
-      <c r="A20" s="72" t="s">
+      <c r="A20" s="55" t="s">
         <v>314</v>
       </c>
-      <c r="B20" s="72"/>
-      <c r="C20" s="72"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="72"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="55"/>
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="D21" s="73">
+      <c r="D21" s="56">
         <f>ROUND(D18*0.1,2)</f>
         <v>21</v>
       </c>
-      <c r="E21" s="73"/>
-      <c r="F21" s="73"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="33" t="s">
         <v>316</v>
       </c>
-      <c r="D22" s="70">
+      <c r="D22" s="52">
         <f>D18+D21</f>
         <v>231</v>
       </c>
-      <c r="E22" s="70"/>
-      <c r="F22" s="70"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -61353,14 +61363,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="53" t="s">
         <v>317</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
     </row>
     <row r="2" spans="1:6" ht="6" customHeight="1">
       <c r="A2" s="76"/>
@@ -61573,13 +61583,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="53" t="s">
         <v>354</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
     </row>
     <row r="2" spans="1:5" ht="6" customHeight="1">
       <c r="A2" s="76"/>
@@ -61918,14 +61928,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="53" t="s">
         <v>392</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
     </row>
     <row r="2" spans="1:6" ht="6" customHeight="1">
       <c r="A2" s="76"/>
